--- a/data/excel/restriction_list_with_real_roads.xlsx
+++ b/data/excel/restriction_list_with_real_roads.xlsx
@@ -335,7 +335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T534"/>
+  <dimension ref="A1:Z534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="3" max="3"/>
@@ -429,15 +429,45 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>実ID</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>番号種別</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>箇所名</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>復旧延長_m</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>幅員_m</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>工事区分</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>道路名称</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>QGIS_ID</t>
         </is>
@@ -17527,7 +17557,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>R-SHOIN-220</t>
+          <t>R-REAL-220</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -17559,14 +17589,10 @@
       <c r="H423" t="n">
         <v>0</v>
       </c>
-      <c r="I423" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 220</t>
-        </is>
-      </c>
+      <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=587m(W=5.3m) 表層工 A=3,111㎡ 上層路盤工 A=3,111㎡ 区画線工 A=482m 側溝工 L=269m 集水桝 N=3箇所</t>
         </is>
       </c>
       <c r="K423" t="n">
@@ -17602,15 +17628,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R423" t="n">
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T423" t="n">
         <v>3902</v>
       </c>
-      <c r="S423" t="inlineStr">
+      <c r="U423" t="inlineStr">
         <is>
           <t>珠洲市正院町正院～川尻 地内</t>
         </is>
       </c>
-      <c r="T423" t="inlineStr">
+      <c r="V423" t="n">
+        <v>587</v>
+      </c>
+      <c r="W423" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>市道171号線</t>
+        </is>
+      </c>
+      <c r="Z423" t="inlineStr">
         <is>
           <t>220</t>
         </is>
@@ -17619,7 +17671,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>R-SHOIN-222</t>
+          <t>R-REAL-222</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -17651,14 +17703,10 @@
       <c r="H424" t="n">
         <v>0</v>
       </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 222</t>
-        </is>
-      </c>
+      <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=672m(W=4.7m) 表層工 A=3,158㎡ 上層路盤工 A=3,158㎡ 防護柵工 L=44m カルバート工 L=5m コンクリート擁壁工 V=11㎥ ブロック積擁壁工 A=52㎡ 側溝工 L=335m 集水桝 N=4箇所</t>
         </is>
       </c>
       <c r="K424" t="n">
@@ -17694,15 +17742,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R424" t="n">
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T424" t="n">
         <v>3904</v>
       </c>
-      <c r="S424" t="inlineStr">
+      <c r="U424" t="inlineStr">
         <is>
           <t>珠洲市正院町正院～小路 地内</t>
         </is>
       </c>
-      <c r="T424" t="inlineStr">
+      <c r="V424" t="n">
+        <v>672</v>
+      </c>
+      <c r="W424" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>市道174号線</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -17711,7 +17785,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>R-SHOIN-223</t>
+          <t>R-REAL-223</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -17743,14 +17817,10 @@
       <c r="H425" t="n">
         <v>0</v>
       </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 223</t>
-        </is>
-      </c>
+      <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=150m(W=3.3m) 表層工 A=495㎡ 上層路盤工 A=488㎡ 側溝工 L=14m</t>
         </is>
       </c>
       <c r="K425" t="n">
@@ -17786,15 +17856,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R425" t="n">
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T425" t="n">
         <v>3944</v>
       </c>
-      <c r="S425" t="inlineStr">
+      <c r="U425" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="T425" t="inlineStr">
+      <c r="V425" t="n">
+        <v>150</v>
+      </c>
+      <c r="W425" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>市道167号線</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
         <is>
           <t>223</t>
         </is>
@@ -17803,7 +17899,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>R-SHOIN-224</t>
+          <t>R-REAL-224</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -17835,14 +17931,10 @@
       <c r="H426" t="n">
         <v>0</v>
       </c>
-      <c r="I426" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 224</t>
-        </is>
-      </c>
+      <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=820m(W=4.1m) 表層工 A=3,362㎡ 上層路盤工（ｔ=10㎝） A=3,071㎡ 上層路盤工（ｔ=15㎝） A=287㎡ 側溝工 L=949m 集水桝工 N=6箇所</t>
         </is>
       </c>
       <c r="K426" t="n">
@@ -17878,15 +17970,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R426" t="n">
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T426" t="n">
         <v>3945</v>
       </c>
-      <c r="S426" t="inlineStr">
+      <c r="U426" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="T426" t="inlineStr">
+      <c r="V426" t="n">
+        <v>820</v>
+      </c>
+      <c r="W426" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>市道168号線</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
         <is>
           <t>224</t>
         </is>
@@ -17895,7 +18013,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>R-SHOIN-225</t>
+          <t>R-REAL-225</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -17927,14 +18045,10 @@
       <c r="H427" t="n">
         <v>0</v>
       </c>
-      <c r="I427" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 225</t>
-        </is>
-      </c>
+      <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,034m(W=3.6m) 表層工 A=3,722㎡ 上層路盤工 A=3,715㎡ 側溝工 L=727m 集水桝工 N=3箇所 コンクリート擁壁工 V=10㎥ 地先境界ブロック工 L=131m 防草コンクリート工 A=48㎡</t>
         </is>
       </c>
       <c r="K427" t="n">
@@ -17970,15 +18084,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R427" t="n">
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T427" t="n">
         <v>3946</v>
       </c>
-      <c r="S427" t="inlineStr">
+      <c r="U427" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="T427" t="inlineStr">
+      <c r="V427" t="n">
+        <v>1034</v>
+      </c>
+      <c r="W427" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>市道169号線</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
         <is>
           <t>225</t>
         </is>
@@ -17987,7 +18127,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>R-SHOIN-226</t>
+          <t>R-REAL-226</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -18019,14 +18159,10 @@
       <c r="H428" t="n">
         <v>0</v>
       </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 226</t>
-        </is>
-      </c>
+      <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=510m(W=7.6m) 表層工 A=3,881㎡ 上層路盤工 A=3,881㎡ 側溝工 L=1,020m 歩車道境界ブロック工 L=209m カーブミラー設置工 N=1基 区画線工 L=80m</t>
         </is>
       </c>
       <c r="K428" t="n">
@@ -18062,15 +18198,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R428" t="n">
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T428" t="n">
         <v>4000</v>
       </c>
-      <c r="S428" t="inlineStr">
+      <c r="U428" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="T428" t="inlineStr">
+      <c r="V428" t="n">
+        <v>510</v>
+      </c>
+      <c r="W428" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>市道166号線</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
         <is>
           <t>226</t>
         </is>
@@ -18079,7 +18241,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>R-SHOIN-227</t>
+          <t>R-REAL-227</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -18111,14 +18273,10 @@
       <c r="H429" t="n">
         <v>0</v>
       </c>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 227</t>
-        </is>
-      </c>
+      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=267m(W=6.4m) 表層工 A=1,709㎡ 上層路盤工 A=1,709㎡ 擁壁工・側溝工・集水桝工・道路付属物設置工一式について調査困難なため未 申請</t>
         </is>
       </c>
       <c r="K429" t="n">
@@ -18154,15 +18312,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R429" t="n">
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T429" t="n">
         <v>4014</v>
       </c>
-      <c r="S429" t="inlineStr">
+      <c r="U429" t="inlineStr">
         <is>
           <t>珠洲市正院町小路～正院 地内</t>
         </is>
       </c>
-      <c r="T429" t="inlineStr">
+      <c r="V429" t="n">
+        <v>267</v>
+      </c>
+      <c r="W429" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>市道164号線</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
         <is>
           <t>227</t>
         </is>
@@ -18171,7 +18355,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>R-SHOIN-228</t>
+          <t>R-REAL-228</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -18203,14 +18387,10 @@
       <c r="H430" t="n">
         <v>0</v>
       </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 228</t>
-        </is>
-      </c>
+      <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K430" t="n">
@@ -18246,15 +18426,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R430" t="n">
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T430" t="n">
         <v>4030</v>
       </c>
-      <c r="S430" t="inlineStr">
+      <c r="U430" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T430" t="inlineStr">
+      <c r="V430" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W430" t="n">
+        <v>4</v>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>市道179号線</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
         <is>
           <t>228</t>
         </is>
@@ -18263,7 +18469,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>R-SHOIN-229</t>
+          <t>R-REAL-229</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -18295,14 +18501,10 @@
       <c r="H431" t="n">
         <v>0</v>
       </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 229</t>
-        </is>
-      </c>
+      <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K431" t="n">
@@ -18338,15 +18540,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R431" t="n">
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T431" t="n">
         <v>4030</v>
       </c>
-      <c r="S431" t="inlineStr">
+      <c r="U431" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T431" t="inlineStr">
+      <c r="V431" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W431" t="n">
+        <v>4</v>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>市道180号線</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
         <is>
           <t>229</t>
         </is>
@@ -18355,7 +18583,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>R-SHOIN-230</t>
+          <t>R-REAL-230</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -18387,14 +18615,10 @@
       <c r="H432" t="n">
         <v>0</v>
       </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 230</t>
-        </is>
-      </c>
+      <c r="I432" t="inlineStr"/>
       <c r="J432" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K432" t="n">
@@ -18430,15 +18654,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R432" t="n">
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T432" t="n">
         <v>4030</v>
       </c>
-      <c r="S432" t="inlineStr">
+      <c r="U432" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T432" t="inlineStr">
+      <c r="V432" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W432" t="n">
+        <v>4</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>市道181号線</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
         <is>
           <t>230</t>
         </is>
@@ -18447,7 +18697,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>R-SHOIN-231</t>
+          <t>R-REAL-231</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -18479,14 +18729,10 @@
       <c r="H433" t="n">
         <v>0</v>
       </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 231</t>
-        </is>
-      </c>
+      <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K433" t="n">
@@ -18522,15 +18768,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R433" t="n">
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T433" t="n">
         <v>4030</v>
       </c>
-      <c r="S433" t="inlineStr">
+      <c r="U433" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T433" t="inlineStr">
+      <c r="V433" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W433" t="n">
+        <v>4</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>市道186号線</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
         <is>
           <t>231</t>
         </is>
@@ -18539,7 +18811,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>R-SHOIN-239</t>
+          <t>R-REAL-239</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -18571,14 +18843,10 @@
       <c r="H434" t="n">
         <v>0</v>
       </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 239</t>
-        </is>
-      </c>
+      <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K434" t="n">
@@ -18614,15 +18882,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R434" t="n">
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T434" t="n">
         <v>4030</v>
       </c>
-      <c r="S434" t="inlineStr">
+      <c r="U434" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T434" t="inlineStr">
+      <c r="V434" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W434" t="n">
+        <v>4</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>市道701号線</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
         <is>
           <t>239</t>
         </is>
@@ -18631,7 +18925,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>R-SHOIN-236</t>
+          <t>R-REAL-236</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -18663,14 +18957,10 @@
       <c r="H435" t="n">
         <v>0</v>
       </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 236</t>
-        </is>
-      </c>
+      <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K435" t="n">
@@ -18706,15 +18996,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R435" t="n">
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T435" t="n">
         <v>4030</v>
       </c>
-      <c r="S435" t="inlineStr">
+      <c r="U435" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T435" t="inlineStr">
+      <c r="V435" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W435" t="n">
+        <v>4</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>市道513号線</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -18723,7 +19039,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>R-SHOIN-238</t>
+          <t>R-REAL-238</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -18755,14 +19071,10 @@
       <c r="H436" t="n">
         <v>0</v>
       </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 238</t>
-        </is>
-      </c>
+      <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K436" t="n">
@@ -18798,15 +19110,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R436" t="n">
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T436" t="n">
         <v>4030</v>
       </c>
-      <c r="S436" t="inlineStr">
+      <c r="U436" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T436" t="inlineStr">
+      <c r="V436" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W436" t="n">
+        <v>4</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>市道546号線</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
         <is>
           <t>238</t>
         </is>
@@ -18815,7 +19153,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>R-SHOIN-232</t>
+          <t>R-REAL-232</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -18847,14 +19185,10 @@
       <c r="H437" t="n">
         <v>0</v>
       </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 232</t>
-        </is>
-      </c>
+      <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K437" t="n">
@@ -18890,15 +19224,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R437" t="n">
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T437" t="n">
         <v>4030</v>
       </c>
-      <c r="S437" t="inlineStr">
+      <c r="U437" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T437" t="inlineStr">
+      <c r="V437" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W437" t="n">
+        <v>4</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>市道187号線</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
         <is>
           <t>232</t>
         </is>
@@ -18907,7 +19267,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>R-SHOIN-237</t>
+          <t>R-REAL-237</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -18939,14 +19299,10 @@
       <c r="H438" t="n">
         <v>0</v>
       </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 237</t>
-        </is>
-      </c>
+      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K438" t="n">
@@ -18982,15 +19338,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R438" t="n">
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T438" t="n">
         <v>4030</v>
       </c>
-      <c r="S438" t="inlineStr">
+      <c r="U438" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T438" t="inlineStr">
+      <c r="V438" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W438" t="n">
+        <v>4</v>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>市道541号線</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
         <is>
           <t>237</t>
         </is>
@@ -18999,7 +19381,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>R-SHOIN-234</t>
+          <t>R-REAL-234</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -19031,14 +19413,10 @@
       <c r="H439" t="n">
         <v>0</v>
       </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 234</t>
-        </is>
-      </c>
+      <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K439" t="n">
@@ -19074,15 +19452,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R439" t="n">
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T439" t="n">
         <v>4030</v>
       </c>
-      <c r="S439" t="inlineStr">
+      <c r="U439" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T439" t="inlineStr">
+      <c r="V439" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W439" t="n">
+        <v>4</v>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>市道192号線</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
         <is>
           <t>234</t>
         </is>
@@ -19091,7 +19495,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>R-SHOIN-235</t>
+          <t>R-REAL-235</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -19123,14 +19527,10 @@
       <c r="H440" t="n">
         <v>0</v>
       </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 235</t>
-        </is>
-      </c>
+      <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K440" t="n">
@@ -19166,15 +19566,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R440" t="n">
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T440" t="n">
         <v>4030</v>
       </c>
-      <c r="S440" t="inlineStr">
+      <c r="U440" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T440" t="inlineStr">
+      <c r="V440" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W440" t="n">
+        <v>4</v>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>市道427号線</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
         <is>
           <t>235</t>
         </is>
@@ -19183,7 +19609,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>R-SHOIN-233</t>
+          <t>R-REAL-233</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -19215,14 +19641,10 @@
       <c r="H441" t="n">
         <v>0</v>
       </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 233</t>
-        </is>
-      </c>
+      <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K441" t="n">
@@ -19258,15 +19680,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R441" t="n">
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T441" t="n">
         <v>4030</v>
       </c>
-      <c r="S441" t="inlineStr">
+      <c r="U441" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T441" t="inlineStr">
+      <c r="V441" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W441" t="n">
+        <v>4</v>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>市道189号線</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
         <is>
           <t>233</t>
         </is>
@@ -19275,7 +19723,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>R-SHOIN-241</t>
+          <t>R-REAL-241</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -19307,14 +19755,10 @@
       <c r="H442" t="n">
         <v>0</v>
       </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 241</t>
-        </is>
-      </c>
+      <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K442" t="n">
@@ -19350,15 +19794,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R442" t="n">
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T442" t="n">
         <v>4030</v>
       </c>
-      <c r="S442" t="inlineStr">
+      <c r="U442" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T442" t="inlineStr">
+      <c r="V442" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W442" t="n">
+        <v>4</v>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>市道712号線</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
         <is>
           <t>241</t>
         </is>
@@ -19367,7 +19837,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>R-SHOIN-240</t>
+          <t>R-REAL-240</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -19399,14 +19869,10 @@
       <c r="H443" t="n">
         <v>0</v>
       </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 240</t>
-        </is>
-      </c>
+      <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,994m(W=4.0m) 表層工 A=7,599㎡ 上層路盤工 A=7,599㎡ 側溝工 L=204m 集水桝工 N=4箇所 コンクリート擁壁工 V=8㎥ ブロック積擁壁工 A=132㎡ 敷砂利工 A=180㎡ コンクリート舗装工 A=99㎡ 法面整形工 A=56㎡ 防護柵工 L=75m 区画線工 L=3,802m 調査不可能箇所については未申請</t>
         </is>
       </c>
       <c r="K443" t="n">
@@ -19442,15 +19908,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R443" t="n">
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T443" t="n">
         <v>4030</v>
       </c>
-      <c r="S443" t="inlineStr">
+      <c r="U443" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T443" t="inlineStr">
+      <c r="V443" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W443" t="n">
+        <v>4</v>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>市道711号線</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
         <is>
           <t>240</t>
         </is>
@@ -19459,7 +19951,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>R-SHOIN-246</t>
+          <t>R-REAL-246</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -19491,14 +19983,10 @@
       <c r="H444" t="n">
         <v>0</v>
       </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 246</t>
-        </is>
-      </c>
+      <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K444" t="n">
@@ -19534,15 +20022,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R444" t="n">
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T444" t="n">
         <v>4092</v>
       </c>
-      <c r="S444" t="inlineStr">
+      <c r="U444" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T444" t="inlineStr">
+      <c r="V444" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W444" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>市道32号線</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
         <is>
           <t>246</t>
         </is>
@@ -19551,7 +20065,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>R-SHOIN-242</t>
+          <t>R-REAL-242</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -19583,14 +20097,10 @@
       <c r="H445" t="n">
         <v>0</v>
       </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 242</t>
-        </is>
-      </c>
+      <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K445" t="n">
@@ -19626,15 +20136,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R445" t="n">
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T445" t="n">
         <v>4092</v>
       </c>
-      <c r="S445" t="inlineStr">
+      <c r="U445" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T445" t="inlineStr">
+      <c r="V445" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W445" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>市道182号線</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
         <is>
           <t>242</t>
         </is>
@@ -19643,7 +20179,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>R-SHOIN-243</t>
+          <t>R-REAL-243</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -19675,14 +20211,10 @@
       <c r="H446" t="n">
         <v>0</v>
       </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 243</t>
-        </is>
-      </c>
+      <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K446" t="n">
@@ -19718,15 +20250,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R446" t="n">
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T446" t="n">
         <v>4092</v>
       </c>
-      <c r="S446" t="inlineStr">
+      <c r="U446" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T446" t="inlineStr">
+      <c r="V446" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W446" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>市道184号線</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
         <is>
           <t>243</t>
         </is>
@@ -19735,7 +20293,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>R-SHOIN-244</t>
+          <t>R-REAL-244</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -19767,14 +20325,10 @@
       <c r="H447" t="n">
         <v>0</v>
       </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 244</t>
-        </is>
-      </c>
+      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K447" t="n">
@@ -19810,15 +20364,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R447" t="n">
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T447" t="n">
         <v>4092</v>
       </c>
-      <c r="S447" t="inlineStr">
+      <c r="U447" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T447" t="inlineStr">
+      <c r="V447" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W447" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>市道188号線</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
         <is>
           <t>244</t>
         </is>
@@ -19827,7 +20407,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>R-SHOIN-245</t>
+          <t>R-REAL-245</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -19859,14 +20439,10 @@
       <c r="H448" t="n">
         <v>0</v>
       </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 245</t>
-        </is>
-      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K448" t="n">
@@ -19902,15 +20478,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R448" t="n">
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T448" t="n">
         <v>4092</v>
       </c>
-      <c r="S448" t="inlineStr">
+      <c r="U448" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T448" t="inlineStr">
+      <c r="V448" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W448" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>市道190号線</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
         <is>
           <t>245</t>
         </is>
@@ -19919,7 +20521,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>R-SHOIN-247</t>
+          <t>R-REAL-247</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -19951,14 +20553,10 @@
       <c r="H449" t="n">
         <v>0</v>
       </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 247</t>
-        </is>
-      </c>
+      <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K449" t="n">
@@ -19994,15 +20592,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R449" t="n">
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T449" t="n">
         <v>4092</v>
       </c>
-      <c r="S449" t="inlineStr">
+      <c r="U449" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T449" t="inlineStr">
+      <c r="V449" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W449" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>市道416号線</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
         <is>
           <t>247</t>
         </is>
@@ -20011,7 +20635,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>R-SHOIN-248</t>
+          <t>R-REAL-248</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -20043,14 +20667,10 @@
       <c r="H450" t="n">
         <v>0</v>
       </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 248</t>
-        </is>
-      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K450" t="n">
@@ -20086,15 +20706,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R450" t="n">
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T450" t="n">
         <v>4092</v>
       </c>
-      <c r="S450" t="inlineStr">
+      <c r="U450" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T450" t="inlineStr">
+      <c r="V450" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W450" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>市道453号線</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
         <is>
           <t>248</t>
         </is>
@@ -20103,7 +20749,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>R-SHOIN-249</t>
+          <t>R-REAL-249</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -20135,14 +20781,10 @@
       <c r="H451" t="n">
         <v>0</v>
       </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 249</t>
-        </is>
-      </c>
+      <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,859ｍ（W=3.5m) 表層工 A=6,563㎡ 上層路盤工 A=6,563㎡ 下層路盤工 A=6,563㎡ 四捨五入はせず数値は入力してください。 区画線工 L=3,718ｍ 側溝工 L=23ｍ 集水桝工 N＝1箇所 ﾌﾞﾛｯｸ積擁壁工 A=281㎡ ｱｽｶｰﾌﾞ工 L=70ｍ 防護柵工 L=270ｍ 掘削工 V=621㎥ 吹付枠工 A=5,408㎡ 鉄筋挿入工 N＝1,352箇所 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K451" t="n">
@@ -20178,15 +20820,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R451" t="n">
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T451" t="n">
         <v>4092</v>
       </c>
-      <c r="S451" t="inlineStr">
+      <c r="U451" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="T451" t="inlineStr">
+      <c r="V451" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W451" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>市道569号線</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
         <is>
           <t>249</t>
         </is>
@@ -20195,7 +20863,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>R-SHOIN-260</t>
+          <t>R-REAL-260</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -20227,14 +20895,10 @@
       <c r="H452" t="n">
         <v>0</v>
       </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 260</t>
-        </is>
-      </c>
+      <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K452" t="n">
@@ -20270,15 +20934,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R452" t="n">
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T452" t="n">
         <v>4159</v>
       </c>
-      <c r="S452" t="inlineStr">
+      <c r="U452" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T452" t="inlineStr">
+      <c r="V452" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W452" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>市道462号線</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
         <is>
           <t>260</t>
         </is>
@@ -20287,7 +20977,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>R-SHOIN-254</t>
+          <t>R-REAL-254</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -20319,14 +21009,10 @@
       <c r="H453" t="n">
         <v>0</v>
       </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 254</t>
-        </is>
-      </c>
+      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K453" t="n">
@@ -20362,15 +21048,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R453" t="n">
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T453" t="n">
         <v>4159</v>
       </c>
-      <c r="S453" t="inlineStr">
+      <c r="U453" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T453" t="inlineStr">
+      <c r="V453" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W453" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>市道170号線</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
         <is>
           <t>254</t>
         </is>
@@ -20379,7 +21091,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>R-SHOIN-255</t>
+          <t>R-REAL-255</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -20411,14 +21123,10 @@
       <c r="H454" t="n">
         <v>0</v>
       </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 255</t>
-        </is>
-      </c>
+      <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K454" t="n">
@@ -20454,15 +21162,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R454" t="n">
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T454" t="n">
         <v>4159</v>
       </c>
-      <c r="S454" t="inlineStr">
+      <c r="U454" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T454" t="inlineStr">
+      <c r="V454" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W454" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>市道172号線</t>
+        </is>
+      </c>
+      <c r="Z454" t="inlineStr">
         <is>
           <t>255</t>
         </is>
@@ -20471,7 +21205,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>R-SHOIN-253</t>
+          <t>R-REAL-253</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -20503,14 +21237,10 @@
       <c r="H455" t="n">
         <v>0</v>
       </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 253</t>
-        </is>
-      </c>
+      <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K455" t="n">
@@ -20546,15 +21276,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R455" t="n">
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T455" t="n">
         <v>4159</v>
       </c>
-      <c r="S455" t="inlineStr">
+      <c r="U455" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T455" t="inlineStr">
+      <c r="V455" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W455" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>市道165号線</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
         <is>
           <t>253</t>
         </is>
@@ -20563,7 +21319,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>R-SHOIN-262</t>
+          <t>R-REAL-262</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -20595,14 +21351,10 @@
       <c r="H456" t="n">
         <v>0</v>
       </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 262</t>
-        </is>
-      </c>
+      <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K456" t="n">
@@ -20638,15 +21390,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R456" t="n">
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T456" t="n">
         <v>4159</v>
       </c>
-      <c r="S456" t="inlineStr">
+      <c r="U456" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T456" t="inlineStr">
+      <c r="V456" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W456" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>市道573号線</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
         <is>
           <t>262</t>
         </is>
@@ -20655,7 +21433,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>R-SHOIN-256</t>
+          <t>R-REAL-256</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -20687,14 +21465,10 @@
       <c r="H457" t="n">
         <v>0</v>
       </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 256</t>
-        </is>
-      </c>
+      <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K457" t="n">
@@ -20730,15 +21504,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R457" t="n">
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T457" t="n">
         <v>4159</v>
       </c>
-      <c r="S457" t="inlineStr">
+      <c r="U457" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T457" t="inlineStr">
+      <c r="V457" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W457" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>市道175号線</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
         <is>
           <t>256</t>
         </is>
@@ -20747,7 +21547,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>R-SHOIN-259</t>
+          <t>R-REAL-259</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -20779,14 +21579,10 @@
       <c r="H458" t="n">
         <v>0</v>
       </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 259</t>
-        </is>
-      </c>
+      <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K458" t="n">
@@ -20822,15 +21618,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R458" t="n">
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T458" t="n">
         <v>4159</v>
       </c>
-      <c r="S458" t="inlineStr">
+      <c r="U458" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T458" t="inlineStr">
+      <c r="V458" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W458" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>市道440号線</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
         <is>
           <t>259</t>
         </is>
@@ -20839,7 +21661,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>R-SHOIN-257</t>
+          <t>R-REAL-257</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -20871,14 +21693,10 @@
       <c r="H459" t="n">
         <v>0</v>
       </c>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 257</t>
-        </is>
-      </c>
+      <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K459" t="n">
@@ -20914,15 +21732,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R459" t="n">
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T459" t="n">
         <v>4159</v>
       </c>
-      <c r="S459" t="inlineStr">
+      <c r="U459" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T459" t="inlineStr">
+      <c r="V459" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W459" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>市道176号線</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
         <is>
           <t>257</t>
         </is>
@@ -20931,7 +21775,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>R-SHOIN-261</t>
+          <t>R-REAL-261</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -20963,14 +21807,10 @@
       <c r="H460" t="n">
         <v>0</v>
       </c>
-      <c r="I460" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 261</t>
-        </is>
-      </c>
+      <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K460" t="n">
@@ -21006,15 +21846,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R460" t="n">
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T460" t="n">
         <v>4159</v>
       </c>
-      <c r="S460" t="inlineStr">
+      <c r="U460" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T460" t="inlineStr">
+      <c r="V460" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W460" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>市道525号線</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
         <is>
           <t>261</t>
         </is>
@@ -21023,7 +21889,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>R-SHOIN-263</t>
+          <t>R-REAL-263</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -21055,14 +21921,10 @@
       <c r="H461" t="n">
         <v>0</v>
       </c>
-      <c r="I461" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 263</t>
-        </is>
-      </c>
+      <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K461" t="n">
@@ -21098,15 +21960,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R461" t="n">
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T461" t="n">
         <v>4159</v>
       </c>
-      <c r="S461" t="inlineStr">
+      <c r="U461" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T461" t="inlineStr">
+      <c r="V461" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W461" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>市道673号線</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
         <is>
           <t>263</t>
         </is>
@@ -21115,7 +22003,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>R-SHOIN-258</t>
+          <t>R-REAL-258</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -21147,14 +22035,10 @@
       <c r="H462" t="n">
         <v>0</v>
       </c>
-      <c r="I462" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 258</t>
-        </is>
-      </c>
+      <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K462" t="n">
@@ -21190,15 +22074,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R462" t="n">
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T462" t="n">
         <v>4159</v>
       </c>
-      <c r="S462" t="inlineStr">
+      <c r="U462" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T462" t="inlineStr">
+      <c r="V462" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W462" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>市道177号線</t>
+        </is>
+      </c>
+      <c r="Z462" t="inlineStr">
         <is>
           <t>258</t>
         </is>
@@ -21207,7 +22117,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>R-SHOIN-250</t>
+          <t>R-REAL-250</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -21239,14 +22149,10 @@
       <c r="H463" t="n">
         <v>0</v>
       </c>
-      <c r="I463" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 250</t>
-        </is>
-      </c>
+      <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=2,774m(W=4.5m) 表層工 A=12,468㎡ 上層路盤工 A=12,468㎡ 下層路盤工 A=12,468㎡ 法面整形工 A=34㎡ 四捨五入はせず数値は入力してください。 区画線工 L=5,516ｍ 側溝工 L=125ｍ 集水桝工 N=6箇所 コンクリート擁壁工 V=37 ㎥ 吹付枠工 A=120㎡ 鉄筋挿入工 N＝30箇所 縁石工 L=8m 防護柵工 L=373m 区間延⾧のうち申請箇所を除く箇所については調査不可のため未申請</t>
         </is>
       </c>
       <c r="K463" t="n">
@@ -21282,15 +22188,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R463" t="n">
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T463" t="n">
         <v>4159</v>
       </c>
-      <c r="S463" t="inlineStr">
+      <c r="U463" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="T463" t="inlineStr">
+      <c r="V463" t="n">
+        <v>2774</v>
+      </c>
+      <c r="W463" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>市道156号線</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
         <is>
           <t>250</t>
         </is>
@@ -21299,7 +22231,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>R-SHOIN-17</t>
+          <t>R-REAL-17</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -21331,14 +22263,10 @@
       <c r="H464" t="n">
         <v>0</v>
       </c>
-      <c r="I464" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 17</t>
-        </is>
-      </c>
+      <c r="I464" t="inlineStr"/>
       <c r="J464" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=4,951ｍ(W=10.4ｍ） 集水桝 N=25箇所 車道舗装工 コンクリート吹付 A=5,320㎡ 表層工 A=51,243㎡ 吹付法枠工 A=5,840㎡ 基層工 A=51,243㎡ コンクリート擁壁 V=112㎡ 上層路盤工 A=51,243㎡ L型擁壁 L=28m 歩道舗装工（Co） 防護柵工 L=138m 表層工 A=1,642㎡ 歩車道境界ブロック L=1,247m 路盤工 A=1,642㎡ カーブミラー N=1基 歩道舗装工（As） 案内標識 N=2基 表層工 A=4,061㎡ 区画線 L=13,931m 路盤工 A=4,061㎡ No.1803～No.2154の歩道部L=351ｍ、 インターロッキング A=350㎡ No.4095～No.4366の歩道部L=271m、 側溝工 L=5,763m 消雪施設一式について、 調査不可能なため未申請</t>
         </is>
       </c>
       <c r="K464" t="n">
@@ -21374,15 +22302,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R464" t="n">
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T464" t="n">
         <v>3987</v>
       </c>
-      <c r="S464" t="inlineStr">
+      <c r="U464" t="inlineStr">
         <is>
           <t>珠洲市宝立町金峰寺～上戸町北方 地内</t>
         </is>
       </c>
-      <c r="T464" t="inlineStr">
+      <c r="V464" t="n">
+        <v>4951</v>
+      </c>
+      <c r="W464" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>市道740号線</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -21391,7 +22345,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>R-SHOIN-18</t>
+          <t>R-REAL-18</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -21423,14 +22377,10 @@
       <c r="H465" t="n">
         <v>0</v>
       </c>
-      <c r="I465" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 18</t>
-        </is>
-      </c>
+      <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=590m(W=6.4m) 表層工 A=3,254㎡ 上層路盤工 A=3,254㎡ 側溝工 L=802m 集水桝 N=5箇所 歩車道境界ブロック L=21m 区画線 L=1,056m</t>
         </is>
       </c>
       <c r="K465" t="n">
@@ -21466,15 +22416,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R465" t="n">
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T465" t="n">
         <v>3948</v>
       </c>
-      <c r="S465" t="inlineStr">
+      <c r="U465" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼 地内</t>
         </is>
       </c>
-      <c r="T465" t="inlineStr">
+      <c r="V465" t="n">
+        <v>590</v>
+      </c>
+      <c r="W465" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>市道70号線</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -21483,7 +22459,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>R-SHOIN-19</t>
+          <t>R-REAL-19</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -21515,14 +22491,10 @@
       <c r="H466" t="n">
         <v>0</v>
       </c>
-      <c r="I466" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 19</t>
-        </is>
-      </c>
+      <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=1,972m(W=3.9m) 表層工 A=7,741㎡ 上層路盤工 A=7,728㎡ 側溝工 L=2,305m 集水桝 N=18箇所 コンクリート擁壁 V=6㎥ 防護柵工 L=128m 地先境界ブロック L=43m 区画線 L=2,650m No.392～No.454 L=62mについて、家屋倒壊により調査不可能なため未申請。</t>
         </is>
       </c>
       <c r="K466" t="n">
@@ -21558,15 +22530,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R466" t="n">
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T466" t="n">
         <v>3949</v>
       </c>
-      <c r="S466" t="inlineStr">
+      <c r="U466" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼～春日野 地内</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr">
+      <c r="V466" t="n">
+        <v>1972</v>
+      </c>
+      <c r="W466" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>市道72号線</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -21575,7 +22573,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>R-SHOIN-20</t>
+          <t>R-REAL-20</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -21607,14 +22605,10 @@
       <c r="H467" t="n">
         <v>0</v>
       </c>
-      <c r="I467" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 20</t>
-        </is>
-      </c>
+      <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=688m(W=6.1m) 表層工 A=4,197㎡ 上層路盤工 A=4,197㎡ 側溝工 L=1,376m 集水桝 N=3箇所 区画線 L=760m</t>
         </is>
       </c>
       <c r="K467" t="n">
@@ -21650,15 +22644,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R467" t="n">
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T467" t="n">
         <v>3950</v>
       </c>
-      <c r="S467" t="inlineStr">
+      <c r="U467" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼 地内</t>
         </is>
       </c>
-      <c r="T467" t="inlineStr">
+      <c r="V467" t="n">
+        <v>688</v>
+      </c>
+      <c r="W467" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>市道438号線</t>
+        </is>
+      </c>
+      <c r="Z467" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -21667,7 +22687,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>R-SHOIN-21</t>
+          <t>R-REAL-21</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -21699,14 +22719,10 @@
       <c r="H468" t="n">
         <v>0</v>
       </c>
-      <c r="I468" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 21</t>
-        </is>
-      </c>
+      <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=331m(W=15.4ｍ) 表層工 A=226㎡ 上層路盤工 A=195㎡ インターロッキング A=2,176㎡ 側溝工 L=570m 集水桝工 N=5箇所 歩車道境界ブロック工 L=38m 地先境界ブロック工 L=373m 区画線工 L=65m</t>
         </is>
       </c>
       <c r="K468" t="n">
@@ -21742,15 +22758,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R468" t="n">
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T468" t="n">
         <v>3969</v>
       </c>
-      <c r="S468" t="inlineStr">
+      <c r="U468" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜島 地内</t>
         </is>
       </c>
-      <c r="T468" t="inlineStr">
+      <c r="V468" t="n">
+        <v>331</v>
+      </c>
+      <c r="W468" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>市道556号線</t>
+        </is>
+      </c>
+      <c r="Z468" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -21759,7 +22801,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>R-SHOIN-23</t>
+          <t>R-REAL-23</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -21791,14 +22833,10 @@
       <c r="H469" t="n">
         <v>0</v>
       </c>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 23</t>
-        </is>
-      </c>
+      <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K469" t="n">
@@ -21834,15 +22872,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R469" t="n">
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T469" t="n">
         <v>4063</v>
       </c>
-      <c r="S469" t="inlineStr">
+      <c r="U469" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T469" t="inlineStr">
+      <c r="V469" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W469" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>市道340号線</t>
+        </is>
+      </c>
+      <c r="Z469" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -21851,7 +22915,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>R-SHOIN-61</t>
+          <t>R-REAL-61</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -21883,14 +22947,10 @@
       <c r="H470" t="n">
         <v>0</v>
       </c>
-      <c r="I470" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 61</t>
-        </is>
-      </c>
+      <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K470" t="n">
@@ -21926,15 +22986,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R470" t="n">
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T470" t="n">
         <v>4063</v>
       </c>
-      <c r="S470" t="inlineStr">
+      <c r="U470" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T470" t="inlineStr">
+      <c r="V470" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W470" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>市道680号線</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -21943,7 +23029,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>R-SHOIN-52</t>
+          <t>R-REAL-52</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -21975,14 +23061,10 @@
       <c r="H471" t="n">
         <v>0</v>
       </c>
-      <c r="I471" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 52</t>
-        </is>
-      </c>
+      <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K471" t="n">
@@ -22018,15 +23100,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R471" t="n">
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T471" t="n">
         <v>4063</v>
       </c>
-      <c r="S471" t="inlineStr">
+      <c r="U471" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T471" t="inlineStr">
+      <c r="V471" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W471" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>市道583号線</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -22035,7 +23143,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>R-SHOIN-58</t>
+          <t>R-REAL-58</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -22067,14 +23175,10 @@
       <c r="H472" t="n">
         <v>0</v>
       </c>
-      <c r="I472" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 58</t>
-        </is>
-      </c>
+      <c r="I472" t="inlineStr"/>
       <c r="J472" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K472" t="n">
@@ -22110,15 +23214,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R472" t="n">
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T472" t="n">
         <v>4063</v>
       </c>
-      <c r="S472" t="inlineStr">
+      <c r="U472" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T472" t="inlineStr">
+      <c r="V472" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W472" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>市道666号線</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -22127,7 +23257,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>R-SHOIN-30</t>
+          <t>R-REAL-30</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -22159,14 +23289,10 @@
       <c r="H473" t="n">
         <v>0</v>
       </c>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 30</t>
-        </is>
-      </c>
+      <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K473" t="n">
@@ -22202,15 +23328,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R473" t="n">
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T473" t="n">
         <v>4063</v>
       </c>
-      <c r="S473" t="inlineStr">
+      <c r="U473" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T473" t="inlineStr">
+      <c r="V473" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W473" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>市道390号線</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -22219,7 +23371,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>R-SHOIN-64</t>
+          <t>R-REAL-64</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -22251,14 +23403,10 @@
       <c r="H474" t="n">
         <v>0</v>
       </c>
-      <c r="I474" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 64</t>
-        </is>
-      </c>
+      <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K474" t="n">
@@ -22294,15 +23442,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R474" t="n">
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T474" t="n">
         <v>4063</v>
       </c>
-      <c r="S474" t="inlineStr">
+      <c r="U474" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T474" t="inlineStr">
+      <c r="V474" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W474" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>市道717号線</t>
+        </is>
+      </c>
+      <c r="Z474" t="inlineStr">
         <is>
           <t>64</t>
         </is>
@@ -22311,7 +23485,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>R-SHOIN-32</t>
+          <t>R-REAL-32</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -22343,14 +23517,10 @@
       <c r="H475" t="n">
         <v>0</v>
       </c>
-      <c r="I475" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 32</t>
-        </is>
-      </c>
+      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K475" t="n">
@@ -22386,15 +23556,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R475" t="n">
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T475" t="n">
         <v>4063</v>
       </c>
-      <c r="S475" t="inlineStr">
+      <c r="U475" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T475" t="inlineStr">
+      <c r="V475" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W475" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>市道394号線</t>
+        </is>
+      </c>
+      <c r="Z475" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -22403,7 +23599,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>R-SHOIN-63</t>
+          <t>R-REAL-63</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -22435,14 +23631,10 @@
       <c r="H476" t="n">
         <v>0</v>
       </c>
-      <c r="I476" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 63</t>
-        </is>
-      </c>
+      <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K476" t="n">
@@ -22478,15 +23670,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R476" t="n">
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T476" t="n">
         <v>4063</v>
       </c>
-      <c r="S476" t="inlineStr">
+      <c r="U476" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T476" t="inlineStr">
+      <c r="V476" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W476" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>市道716号線</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
         <is>
           <t>63</t>
         </is>
@@ -22495,7 +23713,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>R-SHOIN-31</t>
+          <t>R-REAL-31</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -22527,14 +23745,10 @@
       <c r="H477" t="n">
         <v>0</v>
       </c>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 31</t>
-        </is>
-      </c>
+      <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K477" t="n">
@@ -22570,15 +23784,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R477" t="n">
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T477" t="n">
         <v>4063</v>
       </c>
-      <c r="S477" t="inlineStr">
+      <c r="U477" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T477" t="inlineStr">
+      <c r="V477" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W477" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>市道392号線</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -22587,7 +23827,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>R-SHOIN-26</t>
+          <t>R-REAL-26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -22619,14 +23859,10 @@
       <c r="H478" t="n">
         <v>0</v>
       </c>
-      <c r="I478" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 26</t>
-        </is>
-      </c>
+      <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K478" t="n">
@@ -22662,15 +23898,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R478" t="n">
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T478" t="n">
         <v>4063</v>
       </c>
-      <c r="S478" t="inlineStr">
+      <c r="U478" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T478" t="inlineStr">
+      <c r="V478" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W478" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>市道358号線</t>
+        </is>
+      </c>
+      <c r="Z478" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -22679,7 +23941,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>R-SHOIN-37</t>
+          <t>R-REAL-37</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -22711,14 +23973,10 @@
       <c r="H479" t="n">
         <v>0</v>
       </c>
-      <c r="I479" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 37</t>
-        </is>
-      </c>
+      <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K479" t="n">
@@ -22754,15 +24012,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R479" t="n">
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T479" t="n">
         <v>4063</v>
       </c>
-      <c r="S479" t="inlineStr">
+      <c r="U479" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T479" t="inlineStr">
+      <c r="V479" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W479" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>市道422号線</t>
+        </is>
+      </c>
+      <c r="Z479" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -22771,7 +24055,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>R-SHOIN-57</t>
+          <t>R-REAL-57</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -22803,14 +24087,10 @@
       <c r="H480" t="n">
         <v>0</v>
       </c>
-      <c r="I480" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 57</t>
-        </is>
-      </c>
+      <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K480" t="n">
@@ -22846,15 +24126,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R480" t="n">
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T480" t="n">
         <v>4063</v>
       </c>
-      <c r="S480" t="inlineStr">
+      <c r="U480" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T480" t="inlineStr">
+      <c r="V480" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W480" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>市道660号線</t>
+        </is>
+      </c>
+      <c r="Z480" t="inlineStr">
         <is>
           <t>57</t>
         </is>
@@ -22863,7 +24169,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>R-SHOIN-45</t>
+          <t>R-REAL-45</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -22895,14 +24201,10 @@
       <c r="H481" t="n">
         <v>0</v>
       </c>
-      <c r="I481" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 45</t>
-        </is>
-      </c>
+      <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K481" t="n">
@@ -22938,15 +24240,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R481" t="n">
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T481" t="n">
         <v>4063</v>
       </c>
-      <c r="S481" t="inlineStr">
+      <c r="U481" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T481" t="inlineStr">
+      <c r="V481" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W481" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>市道510号線</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -22955,7 +24283,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>R-SHOIN-24</t>
+          <t>R-REAL-24</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -22987,14 +24315,10 @@
       <c r="H482" t="n">
         <v>0</v>
       </c>
-      <c r="I482" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 24</t>
-        </is>
-      </c>
+      <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K482" t="n">
@@ -23030,15 +24354,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R482" t="n">
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T482" t="n">
         <v>4063</v>
       </c>
-      <c r="S482" t="inlineStr">
+      <c r="U482" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T482" t="inlineStr">
+      <c r="V482" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W482" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>市道354号線</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -23047,7 +24397,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>R-SHOIN-33</t>
+          <t>R-REAL-33</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -23079,14 +24429,10 @@
       <c r="H483" t="n">
         <v>0</v>
       </c>
-      <c r="I483" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 33</t>
-        </is>
-      </c>
+      <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K483" t="n">
@@ -23122,15 +24468,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R483" t="n">
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T483" t="n">
         <v>4063</v>
       </c>
-      <c r="S483" t="inlineStr">
+      <c r="U483" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T483" t="inlineStr">
+      <c r="V483" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W483" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>市道417号線</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -23139,7 +24511,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>R-SHOIN-34</t>
+          <t>R-REAL-34</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -23171,14 +24543,10 @@
       <c r="H484" t="n">
         <v>0</v>
       </c>
-      <c r="I484" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 34</t>
-        </is>
-      </c>
+      <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K484" t="n">
@@ -23214,15 +24582,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R484" t="n">
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T484" t="n">
         <v>4063</v>
       </c>
-      <c r="S484" t="inlineStr">
+      <c r="U484" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T484" t="inlineStr">
+      <c r="V484" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W484" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>市道418号線</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -23231,7 +24625,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>R-SHOIN-25</t>
+          <t>R-REAL-25</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -23263,14 +24657,10 @@
       <c r="H485" t="n">
         <v>0</v>
       </c>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 25</t>
-        </is>
-      </c>
+      <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K485" t="n">
@@ -23306,15 +24696,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R485" t="n">
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T485" t="n">
         <v>4063</v>
       </c>
-      <c r="S485" t="inlineStr">
+      <c r="U485" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T485" t="inlineStr">
+      <c r="V485" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W485" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>市道355号線</t>
+        </is>
+      </c>
+      <c r="Z485" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -23323,7 +24739,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>R-SHOIN-54</t>
+          <t>R-REAL-54</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -23355,14 +24771,10 @@
       <c r="H486" t="n">
         <v>0</v>
       </c>
-      <c r="I486" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 54</t>
-        </is>
-      </c>
+      <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K486" t="n">
@@ -23398,15 +24810,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R486" t="n">
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T486" t="n">
         <v>4063</v>
       </c>
-      <c r="S486" t="inlineStr">
+      <c r="U486" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T486" t="inlineStr">
+      <c r="V486" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W486" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y486" t="inlineStr">
+        <is>
+          <t>市道604号線</t>
+        </is>
+      </c>
+      <c r="Z486" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -23415,7 +24853,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>R-SHOIN-65</t>
+          <t>R-REAL-65</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -23447,14 +24885,10 @@
       <c r="H487" t="n">
         <v>0</v>
       </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 65</t>
-        </is>
-      </c>
+      <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K487" t="n">
@@ -23490,15 +24924,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R487" t="n">
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T487" t="n">
         <v>4063</v>
       </c>
-      <c r="S487" t="inlineStr">
+      <c r="U487" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T487" t="inlineStr">
+      <c r="V487" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W487" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y487" t="inlineStr">
+        <is>
+          <t>市道84号線</t>
+        </is>
+      </c>
+      <c r="Z487" t="inlineStr">
         <is>
           <t>65</t>
         </is>
@@ -23507,7 +24967,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>R-SHOIN-39</t>
+          <t>R-REAL-39</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -23539,14 +24999,10 @@
       <c r="H488" t="n">
         <v>0</v>
       </c>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 39</t>
-        </is>
-      </c>
+      <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K488" t="n">
@@ -23582,15 +25038,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R488" t="n">
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T488" t="n">
         <v>4063</v>
       </c>
-      <c r="S488" t="inlineStr">
+      <c r="U488" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T488" t="inlineStr">
+      <c r="V488" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W488" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y488" t="inlineStr">
+        <is>
+          <t>市道433号線</t>
+        </is>
+      </c>
+      <c r="Z488" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -23599,7 +25081,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>R-SHOIN-42</t>
+          <t>R-REAL-42</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -23631,14 +25113,10 @@
       <c r="H489" t="n">
         <v>0</v>
       </c>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 42</t>
-        </is>
-      </c>
+      <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K489" t="n">
@@ -23674,15 +25152,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R489" t="n">
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T489" t="n">
         <v>4063</v>
       </c>
-      <c r="S489" t="inlineStr">
+      <c r="U489" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T489" t="inlineStr">
+      <c r="V489" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W489" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y489" t="inlineStr">
+        <is>
+          <t>市道473号線</t>
+        </is>
+      </c>
+      <c r="Z489" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -23691,7 +25195,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>R-SHOIN-41</t>
+          <t>R-REAL-41</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -23723,14 +25227,10 @@
       <c r="H490" t="n">
         <v>0</v>
       </c>
-      <c r="I490" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 41</t>
-        </is>
-      </c>
+      <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K490" t="n">
@@ -23766,15 +25266,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R490" t="n">
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T490" t="n">
         <v>4063</v>
       </c>
-      <c r="S490" t="inlineStr">
+      <c r="U490" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T490" t="inlineStr">
+      <c r="V490" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W490" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>市道472号線</t>
+        </is>
+      </c>
+      <c r="Z490" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -23783,7 +25309,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>R-SHOIN-49</t>
+          <t>R-REAL-49</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -23815,14 +25341,10 @@
       <c r="H491" t="n">
         <v>0</v>
       </c>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 49</t>
-        </is>
-      </c>
+      <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K491" t="n">
@@ -23858,15 +25380,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R491" t="n">
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T491" t="n">
         <v>4063</v>
       </c>
-      <c r="S491" t="inlineStr">
+      <c r="U491" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T491" t="inlineStr">
+      <c r="V491" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W491" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>市道562号線</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -23875,7 +25423,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>R-SHOIN-28</t>
+          <t>R-REAL-28</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -23907,14 +25455,10 @@
       <c r="H492" t="n">
         <v>0</v>
       </c>
-      <c r="I492" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 28</t>
-        </is>
-      </c>
+      <c r="I492" t="inlineStr"/>
       <c r="J492" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K492" t="n">
@@ -23950,15 +25494,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R492" t="n">
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T492" t="n">
         <v>4063</v>
       </c>
-      <c r="S492" t="inlineStr">
+      <c r="U492" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T492" t="inlineStr">
+      <c r="V492" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W492" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>市道371号線</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -23967,7 +25537,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>R-SHOIN-66</t>
+          <t>R-REAL-66</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -23999,14 +25569,10 @@
       <c r="H493" t="n">
         <v>0</v>
       </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 66</t>
-        </is>
-      </c>
+      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K493" t="n">
@@ -24042,15 +25608,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R493" t="n">
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T493" t="n">
         <v>4063</v>
       </c>
-      <c r="S493" t="inlineStr">
+      <c r="U493" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T493" t="inlineStr">
+      <c r="V493" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W493" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>市道86号線</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
         <is>
           <t>66</t>
         </is>
@@ -24059,7 +25651,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>R-SHOIN-44</t>
+          <t>R-REAL-44</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -24091,14 +25683,10 @@
       <c r="H494" t="n">
         <v>0</v>
       </c>
-      <c r="I494" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 44</t>
-        </is>
-      </c>
+      <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K494" t="n">
@@ -24134,15 +25722,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R494" t="n">
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T494" t="n">
         <v>4063</v>
       </c>
-      <c r="S494" t="inlineStr">
+      <c r="U494" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T494" t="inlineStr">
+      <c r="V494" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W494" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>市道509号線</t>
+        </is>
+      </c>
+      <c r="Z494" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -24151,7 +25765,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>R-SHOIN-36</t>
+          <t>R-REAL-36</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -24183,14 +25797,10 @@
       <c r="H495" t="n">
         <v>0</v>
       </c>
-      <c r="I495" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 36</t>
-        </is>
-      </c>
+      <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K495" t="n">
@@ -24226,15 +25836,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R495" t="n">
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T495" t="n">
         <v>4063</v>
       </c>
-      <c r="S495" t="inlineStr">
+      <c r="U495" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T495" t="inlineStr">
+      <c r="V495" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W495" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>市道421号線</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -24243,7 +25879,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>R-SHOIN-43</t>
+          <t>R-REAL-43</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -24275,14 +25911,10 @@
       <c r="H496" t="n">
         <v>0</v>
       </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 43</t>
-        </is>
-      </c>
+      <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K496" t="n">
@@ -24318,15 +25950,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R496" t="n">
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T496" t="n">
         <v>4063</v>
       </c>
-      <c r="S496" t="inlineStr">
+      <c r="U496" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T496" t="inlineStr">
+      <c r="V496" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W496" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>市道488号線</t>
+        </is>
+      </c>
+      <c r="Z496" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -24335,7 +25993,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>R-SHOIN-67</t>
+          <t>R-REAL-67</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -24367,14 +26025,10 @@
       <c r="H497" t="n">
         <v>0</v>
       </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 67</t>
-        </is>
-      </c>
+      <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K497" t="n">
@@ -24410,15 +26064,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R497" t="n">
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T497" t="n">
         <v>4063</v>
       </c>
-      <c r="S497" t="inlineStr">
+      <c r="U497" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T497" t="inlineStr">
+      <c r="V497" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W497" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>市道88号線</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
         <is>
           <t>67</t>
         </is>
@@ -24427,7 +26107,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>R-SHOIN-38</t>
+          <t>R-REAL-38</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -24459,14 +26139,10 @@
       <c r="H498" t="n">
         <v>0</v>
       </c>
-      <c r="I498" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 38</t>
-        </is>
-      </c>
+      <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K498" t="n">
@@ -24502,15 +26178,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R498" t="n">
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T498" t="n">
         <v>4063</v>
       </c>
-      <c r="S498" t="inlineStr">
+      <c r="U498" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T498" t="inlineStr">
+      <c r="V498" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W498" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>市道429号線</t>
+        </is>
+      </c>
+      <c r="Z498" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -24519,7 +26221,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>R-SHOIN-46</t>
+          <t>R-REAL-46</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -24551,14 +26253,10 @@
       <c r="H499" t="n">
         <v>0</v>
       </c>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 46</t>
-        </is>
-      </c>
+      <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K499" t="n">
@@ -24594,15 +26292,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R499" t="n">
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T499" t="n">
         <v>4063</v>
       </c>
-      <c r="S499" t="inlineStr">
+      <c r="U499" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T499" t="inlineStr">
+      <c r="V499" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W499" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>市道533号線</t>
+        </is>
+      </c>
+      <c r="Z499" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -24611,7 +26335,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>R-SHOIN-47</t>
+          <t>R-REAL-47</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -24643,14 +26367,10 @@
       <c r="H500" t="n">
         <v>0</v>
       </c>
-      <c r="I500" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 47</t>
-        </is>
-      </c>
+      <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K500" t="n">
@@ -24686,15 +26406,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R500" t="n">
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T500" t="n">
         <v>4063</v>
       </c>
-      <c r="S500" t="inlineStr">
+      <c r="U500" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T500" t="inlineStr">
+      <c r="V500" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W500" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>市道534号線</t>
+        </is>
+      </c>
+      <c r="Z500" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -24703,7 +26449,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>R-SHOIN-48</t>
+          <t>R-REAL-48</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -24735,14 +26481,10 @@
       <c r="H501" t="n">
         <v>0</v>
       </c>
-      <c r="I501" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 48</t>
-        </is>
-      </c>
+      <c r="I501" t="inlineStr"/>
       <c r="J501" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K501" t="n">
@@ -24778,15 +26520,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R501" t="n">
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T501" t="n">
         <v>4063</v>
       </c>
-      <c r="S501" t="inlineStr">
+      <c r="U501" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T501" t="inlineStr">
+      <c r="V501" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W501" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>市道538号線</t>
+        </is>
+      </c>
+      <c r="Z501" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -24795,7 +26563,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>R-SHOIN-309</t>
+          <t>R-REAL-309</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -24827,11 +26595,7 @@
       <c r="H502" t="n">
         <v>0</v>
       </c>
-      <c r="I502" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 309</t>
-        </is>
-      </c>
+      <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr">
         <is>
           <t>道路復旧</t>
@@ -24862,15 +26626,39 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R502" t="n">
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T502" t="n">
         <v>4063</v>
       </c>
-      <c r="S502" t="inlineStr">
+      <c r="U502" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T502" t="inlineStr">
+      <c r="V502" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W502" t="inlineStr"/>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>市道544号線</t>
+        </is>
+      </c>
+      <c r="Z502" t="inlineStr">
         <is>
           <t>309</t>
         </is>
@@ -24879,7 +26667,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>R-SHOIN-60</t>
+          <t>R-REAL-60</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -24911,14 +26699,10 @@
       <c r="H503" t="n">
         <v>0</v>
       </c>
-      <c r="I503" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 60</t>
-        </is>
-      </c>
+      <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K503" t="n">
@@ -24954,15 +26738,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R503" t="n">
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T503" t="n">
         <v>4063</v>
       </c>
-      <c r="S503" t="inlineStr">
+      <c r="U503" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T503" t="inlineStr">
+      <c r="V503" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W503" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>市道677号線</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -24971,7 +26781,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>R-SHOIN-51</t>
+          <t>R-REAL-51</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -25003,14 +26813,10 @@
       <c r="H504" t="n">
         <v>0</v>
       </c>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 51</t>
-        </is>
-      </c>
+      <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K504" t="n">
@@ -25046,15 +26852,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R504" t="n">
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T504" t="n">
         <v>4063</v>
       </c>
-      <c r="S504" t="inlineStr">
+      <c r="U504" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T504" t="inlineStr">
+      <c r="V504" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W504" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>市道580号線</t>
+        </is>
+      </c>
+      <c r="Z504" t="inlineStr">
         <is>
           <t>51</t>
         </is>
@@ -25063,7 +26895,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>R-SHOIN-50</t>
+          <t>R-REAL-50</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -25095,14 +26927,10 @@
       <c r="H505" t="n">
         <v>0</v>
       </c>
-      <c r="I505" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 50</t>
-        </is>
-      </c>
+      <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K505" t="n">
@@ -25138,15 +26966,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R505" t="n">
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T505" t="n">
         <v>4063</v>
       </c>
-      <c r="S505" t="inlineStr">
+      <c r="U505" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T505" t="inlineStr">
+      <c r="V505" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W505" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>市道575号線</t>
+        </is>
+      </c>
+      <c r="Z505" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -25155,7 +27009,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>R-SHOIN-55</t>
+          <t>R-REAL-55</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -25187,14 +27041,10 @@
       <c r="H506" t="n">
         <v>0</v>
       </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 55</t>
-        </is>
-      </c>
+      <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K506" t="n">
@@ -25230,15 +27080,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R506" t="n">
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T506" t="n">
         <v>4063</v>
       </c>
-      <c r="S506" t="inlineStr">
+      <c r="U506" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T506" t="inlineStr">
+      <c r="V506" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W506" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>市道650号線</t>
+        </is>
+      </c>
+      <c r="Z506" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -25247,7 +27123,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>R-SHOIN-59</t>
+          <t>R-REAL-59</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -25279,14 +27155,10 @@
       <c r="H507" t="n">
         <v>0</v>
       </c>
-      <c r="I507" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 59</t>
-        </is>
-      </c>
+      <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K507" t="n">
@@ -25322,15 +27194,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R507" t="n">
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T507" t="n">
         <v>4063</v>
       </c>
-      <c r="S507" t="inlineStr">
+      <c r="U507" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T507" t="inlineStr">
+      <c r="V507" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W507" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>市道674号線</t>
+        </is>
+      </c>
+      <c r="Z507" t="inlineStr">
         <is>
           <t>59</t>
         </is>
@@ -25339,7 +27237,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>R-SHOIN-40</t>
+          <t>R-REAL-40</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -25371,14 +27269,10 @@
       <c r="H508" t="n">
         <v>0</v>
       </c>
-      <c r="I508" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 40</t>
-        </is>
-      </c>
+      <c r="I508" t="inlineStr"/>
       <c r="J508" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K508" t="n">
@@ -25414,15 +27308,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R508" t="n">
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T508" t="n">
         <v>4063</v>
       </c>
-      <c r="S508" t="inlineStr">
+      <c r="U508" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T508" t="inlineStr">
+      <c r="V508" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W508" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>市道471号線</t>
+        </is>
+      </c>
+      <c r="Z508" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -25431,7 +27351,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>R-SHOIN-53</t>
+          <t>R-REAL-53</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -25463,14 +27383,10 @@
       <c r="H509" t="n">
         <v>0</v>
       </c>
-      <c r="I509" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 53</t>
-        </is>
-      </c>
+      <c r="I509" t="inlineStr"/>
       <c r="J509" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K509" t="n">
@@ -25506,15 +27422,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R509" t="n">
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T509" t="n">
         <v>4063</v>
       </c>
-      <c r="S509" t="inlineStr">
+      <c r="U509" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T509" t="inlineStr">
+      <c r="V509" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W509" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>市道603号線</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
         <is>
           <t>53</t>
         </is>
@@ -25523,7 +27465,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>R-SHOIN-56</t>
+          <t>R-REAL-56</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -25555,14 +27497,10 @@
       <c r="H510" t="n">
         <v>0</v>
       </c>
-      <c r="I510" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 56</t>
-        </is>
-      </c>
+      <c r="I510" t="inlineStr"/>
       <c r="J510" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K510" t="n">
@@ -25598,15 +27536,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R510" t="n">
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T510" t="n">
         <v>4063</v>
       </c>
-      <c r="S510" t="inlineStr">
+      <c r="U510" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T510" t="inlineStr">
+      <c r="V510" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W510" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>市道656号線</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
         <is>
           <t>56</t>
         </is>
@@ -25615,7 +27579,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>R-SHOIN-62</t>
+          <t>R-REAL-62</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -25647,14 +27611,10 @@
       <c r="H511" t="n">
         <v>0</v>
       </c>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 62</t>
-        </is>
-      </c>
+      <c r="I511" t="inlineStr"/>
       <c r="J511" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K511" t="n">
@@ -25690,15 +27650,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R511" t="n">
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T511" t="n">
         <v>4063</v>
       </c>
-      <c r="S511" t="inlineStr">
+      <c r="U511" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T511" t="inlineStr">
+      <c r="V511" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W511" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>市道686号線</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -25707,7 +27693,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>R-SHOIN-27</t>
+          <t>R-REAL-27</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -25739,14 +27725,10 @@
       <c r="H512" t="n">
         <v>0</v>
       </c>
-      <c r="I512" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 27</t>
-        </is>
-      </c>
+      <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,081m(W=3.9m) 表層工 A=19,938㎡ 上層路盤工 A=19,938㎡ 区画線工 L=10,162m 法面整形 A=15㎡ 側溝工 L=264m 集水桝 N=3箇所 プレキャスト擁壁 L=20m コンクリート擁壁 V=85㎥ ブロック積擁壁 A=130㎡ 縁石工 L=5m 防護柵工 L=116m</t>
         </is>
       </c>
       <c r="K512" t="n">
@@ -25782,15 +27764,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R512" t="n">
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T512" t="n">
         <v>4063</v>
       </c>
-      <c r="S512" t="inlineStr">
+      <c r="U512" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T512" t="inlineStr">
+      <c r="V512" t="n">
+        <v>5081</v>
+      </c>
+      <c r="W512" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>市道363号線</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -25799,7 +27807,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>R-SHOIN-86</t>
+          <t>R-REAL-86</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -25831,14 +27839,10 @@
       <c r="H513" t="n">
         <v>0</v>
       </c>
-      <c r="I513" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 86</t>
-        </is>
-      </c>
+      <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K513" t="n">
@@ -25874,15 +27878,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R513" t="n">
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T513" t="n">
         <v>4064</v>
       </c>
-      <c r="S513" t="inlineStr">
+      <c r="U513" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T513" t="inlineStr">
+      <c r="V513" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W513" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>市道79号線</t>
+        </is>
+      </c>
+      <c r="Z513" t="inlineStr">
         <is>
           <t>86</t>
         </is>
@@ -25891,7 +27921,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>R-SHOIN-87</t>
+          <t>R-REAL-87</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -25923,14 +27953,10 @@
       <c r="H514" t="n">
         <v>0</v>
       </c>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 87</t>
-        </is>
-      </c>
+      <c r="I514" t="inlineStr"/>
       <c r="J514" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K514" t="n">
@@ -25966,15 +27992,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R514" t="n">
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T514" t="n">
         <v>4064</v>
       </c>
-      <c r="S514" t="inlineStr">
+      <c r="U514" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T514" t="inlineStr">
+      <c r="V514" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W514" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>市道80号線</t>
+        </is>
+      </c>
+      <c r="Z514" t="inlineStr">
         <is>
           <t>87</t>
         </is>
@@ -25983,7 +28035,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>R-SHOIN-85</t>
+          <t>R-REAL-85</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -26015,14 +28067,10 @@
       <c r="H515" t="n">
         <v>0</v>
       </c>
-      <c r="I515" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 85</t>
-        </is>
-      </c>
+      <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K515" t="n">
@@ -26058,15 +28106,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R515" t="n">
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T515" t="n">
         <v>4064</v>
       </c>
-      <c r="S515" t="inlineStr">
+      <c r="U515" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T515" t="inlineStr">
+      <c r="V515" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W515" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>市道78号線</t>
+        </is>
+      </c>
+      <c r="Z515" t="inlineStr">
         <is>
           <t>85</t>
         </is>
@@ -26075,7 +28149,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>R-SHOIN-84</t>
+          <t>R-REAL-84</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -26107,14 +28181,10 @@
       <c r="H516" t="n">
         <v>0</v>
       </c>
-      <c r="I516" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 84</t>
-        </is>
-      </c>
+      <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K516" t="n">
@@ -26150,15 +28220,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R516" t="n">
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T516" t="n">
         <v>4064</v>
       </c>
-      <c r="S516" t="inlineStr">
+      <c r="U516" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T516" t="inlineStr">
+      <c r="V516" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W516" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>市道77号線</t>
+        </is>
+      </c>
+      <c r="Z516" t="inlineStr">
         <is>
           <t>84</t>
         </is>
@@ -26167,7 +28263,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>R-SHOIN-83</t>
+          <t>R-REAL-83</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -26199,14 +28295,10 @@
       <c r="H517" t="n">
         <v>0</v>
       </c>
-      <c r="I517" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 83</t>
-        </is>
-      </c>
+      <c r="I517" t="inlineStr"/>
       <c r="J517" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K517" t="n">
@@ -26242,15 +28334,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R517" t="n">
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T517" t="n">
         <v>4064</v>
       </c>
-      <c r="S517" t="inlineStr">
+      <c r="U517" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T517" t="inlineStr">
+      <c r="V517" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W517" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>市道76号線</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr">
         <is>
           <t>83</t>
         </is>
@@ -26259,7 +28377,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>R-SHOIN-310</t>
+          <t>R-REAL-310</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -26291,11 +28409,7 @@
       <c r="H518" t="n">
         <v>0</v>
       </c>
-      <c r="I518" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 310</t>
-        </is>
-      </c>
+      <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr">
         <is>
           <t>道路復旧</t>
@@ -26324,15 +28438,37 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R518" t="n">
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T518" t="n">
         <v>4064</v>
       </c>
-      <c r="S518" t="inlineStr">
+      <c r="U518" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T518" t="inlineStr">
+      <c r="V518" t="inlineStr"/>
+      <c r="W518" t="inlineStr"/>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>市道73号線</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr">
         <is>
           <t>310</t>
         </is>
@@ -26341,7 +28477,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>R-SHOIN-82</t>
+          <t>R-REAL-82</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -26373,14 +28509,10 @@
       <c r="H519" t="n">
         <v>0</v>
       </c>
-      <c r="I519" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 82</t>
-        </is>
-      </c>
+      <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K519" t="n">
@@ -26416,15 +28548,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R519" t="n">
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T519" t="n">
         <v>4064</v>
       </c>
-      <c r="S519" t="inlineStr">
+      <c r="U519" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T519" t="inlineStr">
+      <c r="V519" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W519" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>市道75号線</t>
+        </is>
+      </c>
+      <c r="Z519" t="inlineStr">
         <is>
           <t>82</t>
         </is>
@@ -26433,7 +28591,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>R-SHOIN-68</t>
+          <t>R-REAL-68</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -26465,14 +28623,10 @@
       <c r="H520" t="n">
         <v>0</v>
       </c>
-      <c r="I520" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 68</t>
-        </is>
-      </c>
+      <c r="I520" t="inlineStr"/>
       <c r="J520" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K520" t="n">
@@ -26508,15 +28662,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R520" t="n">
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T520" t="n">
         <v>4064</v>
       </c>
-      <c r="S520" t="inlineStr">
+      <c r="U520" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T520" t="inlineStr">
+      <c r="V520" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W520" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>市道13号線</t>
+        </is>
+      </c>
+      <c r="Z520" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -26525,7 +28705,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>R-SHOIN-77</t>
+          <t>R-REAL-77</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -26557,14 +28737,10 @@
       <c r="H521" t="n">
         <v>0</v>
       </c>
-      <c r="I521" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 77</t>
-        </is>
-      </c>
+      <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K521" t="n">
@@ -26600,15 +28776,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R521" t="n">
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T521" t="n">
         <v>4064</v>
       </c>
-      <c r="S521" t="inlineStr">
+      <c r="U521" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T521" t="inlineStr">
+      <c r="V521" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W521" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>市道69号線</t>
+        </is>
+      </c>
+      <c r="Z521" t="inlineStr">
         <is>
           <t>77</t>
         </is>
@@ -26617,7 +28819,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>R-SHOIN-76</t>
+          <t>R-REAL-76</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -26649,14 +28851,10 @@
       <c r="H522" t="n">
         <v>0</v>
       </c>
-      <c r="I522" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 76</t>
-        </is>
-      </c>
+      <c r="I522" t="inlineStr"/>
       <c r="J522" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K522" t="n">
@@ -26692,15 +28890,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R522" t="n">
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T522" t="n">
         <v>4064</v>
       </c>
-      <c r="S522" t="inlineStr">
+      <c r="U522" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T522" t="inlineStr">
+      <c r="V522" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W522" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>市道68号線</t>
+        </is>
+      </c>
+      <c r="Z522" t="inlineStr">
         <is>
           <t>76</t>
         </is>
@@ -26709,7 +28933,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>R-SHOIN-73</t>
+          <t>R-REAL-73</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -26741,14 +28965,10 @@
       <c r="H523" t="n">
         <v>0</v>
       </c>
-      <c r="I523" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 73</t>
-        </is>
-      </c>
+      <c r="I523" t="inlineStr"/>
       <c r="J523" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K523" t="n">
@@ -26784,15 +29004,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R523" t="n">
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T523" t="n">
         <v>4064</v>
       </c>
-      <c r="S523" t="inlineStr">
+      <c r="U523" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T523" t="inlineStr">
+      <c r="V523" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W523" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>市道64号線</t>
+        </is>
+      </c>
+      <c r="Z523" t="inlineStr">
         <is>
           <t>73</t>
         </is>
@@ -26801,7 +29047,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>R-SHOIN-74</t>
+          <t>R-REAL-74</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -26833,14 +29079,10 @@
       <c r="H524" t="n">
         <v>0</v>
       </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 74</t>
-        </is>
-      </c>
+      <c r="I524" t="inlineStr"/>
       <c r="J524" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K524" t="n">
@@ -26876,15 +29118,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R524" t="n">
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T524" t="n">
         <v>4064</v>
       </c>
-      <c r="S524" t="inlineStr">
+      <c r="U524" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T524" t="inlineStr">
+      <c r="V524" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W524" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>市道65号線</t>
+        </is>
+      </c>
+      <c r="Z524" t="inlineStr">
         <is>
           <t>74</t>
         </is>
@@ -26893,7 +29161,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>R-SHOIN-72</t>
+          <t>R-REAL-72</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -26925,14 +29193,10 @@
       <c r="H525" t="n">
         <v>0</v>
       </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 72</t>
-        </is>
-      </c>
+      <c r="I525" t="inlineStr"/>
       <c r="J525" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K525" t="n">
@@ -26968,15 +29232,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R525" t="n">
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T525" t="n">
         <v>4064</v>
       </c>
-      <c r="S525" t="inlineStr">
+      <c r="U525" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T525" t="inlineStr">
+      <c r="V525" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W525" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>市道61号線</t>
+        </is>
+      </c>
+      <c r="Z525" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -26985,7 +29275,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>R-SHOIN-70</t>
+          <t>R-REAL-70</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -27017,14 +29307,10 @@
       <c r="H526" t="n">
         <v>0</v>
       </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 70</t>
-        </is>
-      </c>
+      <c r="I526" t="inlineStr"/>
       <c r="J526" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K526" t="n">
@@ -27060,15 +29346,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R526" t="n">
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T526" t="n">
         <v>4064</v>
       </c>
-      <c r="S526" t="inlineStr">
+      <c r="U526" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T526" t="inlineStr">
+      <c r="V526" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W526" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>市道59号線</t>
+        </is>
+      </c>
+      <c r="Z526" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -27077,7 +29389,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>R-SHOIN-69</t>
+          <t>R-REAL-69</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -27109,14 +29421,10 @@
       <c r="H527" t="n">
         <v>0</v>
       </c>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 69</t>
-        </is>
-      </c>
+      <c r="I527" t="inlineStr"/>
       <c r="J527" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K527" t="n">
@@ -27152,15 +29460,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R527" t="n">
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T527" t="n">
         <v>4064</v>
       </c>
-      <c r="S527" t="inlineStr">
+      <c r="U527" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T527" t="inlineStr">
+      <c r="V527" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W527" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>市道58号線</t>
+        </is>
+      </c>
+      <c r="Z527" t="inlineStr">
         <is>
           <t>69</t>
         </is>
@@ -27169,7 +29503,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>R-SHOIN-88</t>
+          <t>R-REAL-88</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -27201,14 +29535,10 @@
       <c r="H528" t="n">
         <v>0</v>
       </c>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 88</t>
-        </is>
-      </c>
+      <c r="I528" t="inlineStr"/>
       <c r="J528" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K528" t="n">
@@ -27244,15 +29574,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R528" t="n">
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T528" t="n">
         <v>4064</v>
       </c>
-      <c r="S528" t="inlineStr">
+      <c r="U528" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T528" t="inlineStr">
+      <c r="V528" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W528" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>市道83号線</t>
+        </is>
+      </c>
+      <c r="Z528" t="inlineStr">
         <is>
           <t>88</t>
         </is>
@@ -27261,7 +29617,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>R-SHOIN-79</t>
+          <t>R-REAL-79</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -27293,14 +29649,10 @@
       <c r="H529" t="n">
         <v>0</v>
       </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 79</t>
-        </is>
-      </c>
+      <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K529" t="n">
@@ -27336,15 +29688,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R529" t="n">
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T529" t="n">
         <v>4064</v>
       </c>
-      <c r="S529" t="inlineStr">
+      <c r="U529" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T529" t="inlineStr">
+      <c r="V529" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W529" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>市道736号線</t>
+        </is>
+      </c>
+      <c r="Z529" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -27353,7 +29731,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>R-SHOIN-93</t>
+          <t>R-REAL-93</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -27385,14 +29763,10 @@
       <c r="H530" t="n">
         <v>0</v>
       </c>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 93</t>
-        </is>
-      </c>
+      <c r="I530" t="inlineStr"/>
       <c r="J530" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>アスファルト舗装工 A=147m2 カラーアスファルト舗装工 A=569m2 インターロッキングブロック舗装工 A=262m2 玉砂利舗装工 A=324m2 タイル舗装工 A=359m2</t>
         </is>
       </c>
       <c r="K530" t="inlineStr"/>
@@ -27418,15 +29792,37 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R530" t="n">
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T530" t="n">
         <v>67</v>
       </c>
-      <c r="S530" t="inlineStr">
+      <c r="U530" t="inlineStr">
         <is>
           <t>見付公園</t>
         </is>
       </c>
-      <c r="T530" t="inlineStr">
+      <c r="V530" t="inlineStr"/>
+      <c r="W530" t="inlineStr"/>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>公園復旧工事</t>
+        </is>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>67 見付公園</t>
+        </is>
+      </c>
+      <c r="Z530" t="inlineStr">
         <is>
           <t>93</t>
         </is>
@@ -27435,7 +29831,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>R-SHOIN-78</t>
+          <t>R-REAL-78</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -27467,14 +29863,10 @@
       <c r="H531" t="n">
         <v>0</v>
       </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 78</t>
-        </is>
-      </c>
+      <c r="I531" t="inlineStr"/>
       <c r="J531" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K531" t="n">
@@ -27510,15 +29902,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R531" t="n">
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T531" t="n">
         <v>4064</v>
       </c>
-      <c r="S531" t="inlineStr">
+      <c r="U531" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T531" t="inlineStr">
+      <c r="V531" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W531" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>市道71号線</t>
+        </is>
+      </c>
+      <c r="Z531" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -27527,7 +29945,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>R-SHOIN-71</t>
+          <t>R-REAL-71</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -27559,14 +29977,10 @@
       <c r="H532" t="n">
         <v>0</v>
       </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 71</t>
-        </is>
-      </c>
+      <c r="I532" t="inlineStr"/>
       <c r="J532" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=5,854m(W=4.2m) 表層工 A=24,764㎡ 上層路盤工 A=24,764㎡ 区画線工 L=11,708m 側溝工 L=308m 集水桝 N=16箇所 コンクリート擁壁 V=2㎥ ブロック積擁壁 A=4㎡ アスカーブ L=77m 縁石工 L=7m 防草コンクリート A=25㎡ 防護柵工 L=292m 調査不可能箇所について未申請</t>
         </is>
       </c>
       <c r="K532" t="n">
@@ -27602,15 +30016,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R532" t="n">
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T532" t="n">
         <v>4064</v>
       </c>
-      <c r="S532" t="inlineStr">
+      <c r="U532" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="T532" t="inlineStr">
+      <c r="V532" t="n">
+        <v>5854</v>
+      </c>
+      <c r="W532" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>市道60号線</t>
+        </is>
+      </c>
+      <c r="Z532" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -27619,7 +30059,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>R-SHOIN-15</t>
+          <t>R-REAL-15</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -27651,14 +30091,10 @@
       <c r="H533" t="n">
         <v>0</v>
       </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 15</t>
-        </is>
-      </c>
+      <c r="I533" t="inlineStr"/>
       <c r="J533" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=828m(W=6.2m) 表層工 A=5,696㎡ 上層路盤工 A=5,650㎡ 下層路盤工 A=439㎡ 側溝工 L=6m 集水桝 N=1箇所 ブロック積擁壁 A=150㎡ 防護柵工 L=50m No.0～No.36 L=36mについて、調査不可能なため未申請。</t>
         </is>
       </c>
       <c r="K533" t="n">
@@ -27694,15 +30130,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R533" t="n">
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T533" t="n">
         <v>3889</v>
       </c>
-      <c r="S533" t="inlineStr">
+      <c r="U533" t="inlineStr">
         <is>
           <t>珠洲市宝立町春日野 地内</t>
         </is>
       </c>
-      <c r="T533" t="inlineStr">
+      <c r="V533" t="n">
+        <v>828</v>
+      </c>
+      <c r="W533" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>市道10号線</t>
+        </is>
+      </c>
+      <c r="Z533" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -27711,7 +30173,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>R-SHOIN-16</t>
+          <t>R-REAL-16</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -27743,14 +30205,10 @@
       <c r="H534" t="n">
         <v>0</v>
       </c>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>QGIS real geometry / 正院 / ID 16</t>
-        </is>
-      </c>
+      <c r="I534" t="inlineStr"/>
       <c r="J534" t="inlineStr">
         <is>
-          <t>道路復旧</t>
+          <t>復旧延⾧ L=514ｍ(W=11.1m) 表層工 A=6,228㎡ 上層路盤工 A=6,221㎡ インターロッキング A=546㎡ 側溝工 L=96m 集水桝 N=3箇所 歩車道境界ブロック L=10m 区画線 L=1,542m</t>
         </is>
       </c>
       <c r="K534" t="n">
@@ -27786,15 +30244,41 @@
           <t>施工予定</t>
         </is>
       </c>
-      <c r="R534" t="n">
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>査定番号</t>
+        </is>
+      </c>
+      <c r="T534" t="n">
         <v>3892</v>
       </c>
-      <c r="S534" t="inlineStr">
+      <c r="U534" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜島～鵜飼 地内</t>
         </is>
       </c>
-      <c r="T534" t="inlineStr">
+      <c r="V534" t="n">
+        <v>514</v>
+      </c>
+      <c r="W534" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>道路復旧工事</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>市道52-2号線</t>
+        </is>
+      </c>
+      <c r="Z534" t="inlineStr">
         <is>
           <t>16</t>
         </is>

--- a/data/excel/restriction_list_with_real_roads.xlsx
+++ b/data/excel/restriction_list_with_real_roads.xlsx
@@ -335,7 +335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z534"/>
+  <dimension ref="A1:AA534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="3" max="3"/>
@@ -429,45 +429,50 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>項目状態</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>実ID</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>番号種別</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>箇所名</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>復旧延長_m</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>幅員_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>工事区分</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>道路名称</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>QGIS_ID</t>
         </is>
@@ -17565,16 +17570,8 @@
           <t>市道171号線</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" s="3" t="n">
         <v>46218</v>
       </c>
@@ -17630,39 +17627,44 @@
       </c>
       <c r="R423" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="S423" t="inlineStr">
+      <c r="T423" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T423" t="n">
+      <c r="U423" t="n">
         <v>3902</v>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="V423" t="inlineStr">
         <is>
           <t>珠洲市正院町正院～川尻 地内</t>
         </is>
       </c>
-      <c r="V423" t="n">
+      <c r="W423" t="n">
         <v>587</v>
       </c>
-      <c r="W423" t="n">
+      <c r="X423" t="n">
         <v>5.3</v>
       </c>
-      <c r="X423" t="inlineStr">
+      <c r="Y423" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y423" t="inlineStr">
+      <c r="Z423" t="inlineStr">
         <is>
           <t>市道171号線</t>
         </is>
       </c>
-      <c r="Z423" t="inlineStr">
+      <c r="AA423" t="inlineStr">
         <is>
           <t>220</t>
         </is>
@@ -17679,16 +17681,8 @@
           <t>市道174号線</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" s="3" t="n">
         <v>46218</v>
       </c>
@@ -17744,39 +17738,44 @@
       </c>
       <c r="R424" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="S424" t="inlineStr">
+      <c r="T424" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T424" t="n">
+      <c r="U424" t="n">
         <v>3904</v>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="V424" t="inlineStr">
         <is>
           <t>珠洲市正院町正院～小路 地内</t>
         </is>
       </c>
-      <c r="V424" t="n">
+      <c r="W424" t="n">
         <v>672</v>
       </c>
-      <c r="W424" t="n">
+      <c r="X424" t="n">
         <v>4.7</v>
       </c>
-      <c r="X424" t="inlineStr">
+      <c r="Y424" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y424" t="inlineStr">
+      <c r="Z424" t="inlineStr">
         <is>
           <t>市道174号線</t>
         </is>
       </c>
-      <c r="Z424" t="inlineStr">
+      <c r="AA424" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -17793,16 +17792,8 @@
           <t>市道167号線</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" s="3" t="n">
         <v>46218</v>
       </c>
@@ -17858,39 +17849,44 @@
       </c>
       <c r="R425" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="S425" t="inlineStr">
+      <c r="T425" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T425" t="n">
+      <c r="U425" t="n">
         <v>3944</v>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="V425" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="V425" t="n">
+      <c r="W425" t="n">
         <v>150</v>
       </c>
-      <c r="W425" t="n">
+      <c r="X425" t="n">
         <v>3.3</v>
       </c>
-      <c r="X425" t="inlineStr">
+      <c r="Y425" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y425" t="inlineStr">
+      <c r="Z425" t="inlineStr">
         <is>
           <t>市道167号線</t>
         </is>
       </c>
-      <c r="Z425" t="inlineStr">
+      <c r="AA425" t="inlineStr">
         <is>
           <t>223</t>
         </is>
@@ -17907,16 +17903,8 @@
           <t>市道168号線</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" s="3" t="n">
         <v>46218</v>
       </c>
@@ -17972,39 +17960,44 @@
       </c>
       <c r="R426" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="S426" t="inlineStr">
+      <c r="T426" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T426" t="n">
+      <c r="U426" t="n">
         <v>3945</v>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="V426" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="V426" t="n">
+      <c r="W426" t="n">
         <v>820</v>
       </c>
-      <c r="W426" t="n">
+      <c r="X426" t="n">
         <v>4.1</v>
       </c>
-      <c r="X426" t="inlineStr">
+      <c r="Y426" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y426" t="inlineStr">
+      <c r="Z426" t="inlineStr">
         <is>
           <t>市道168号線</t>
         </is>
       </c>
-      <c r="Z426" t="inlineStr">
+      <c r="AA426" t="inlineStr">
         <is>
           <t>224</t>
         </is>
@@ -18021,16 +18014,8 @@
           <t>市道169号線</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18086,39 +18071,44 @@
       </c>
       <c r="R427" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="S427" t="inlineStr">
+      <c r="T427" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T427" t="n">
+      <c r="U427" t="n">
         <v>3946</v>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="V427" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="V427" t="n">
+      <c r="W427" t="n">
         <v>1034</v>
       </c>
-      <c r="W427" t="n">
+      <c r="X427" t="n">
         <v>3.6</v>
       </c>
-      <c r="X427" t="inlineStr">
+      <c r="Y427" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y427" t="inlineStr">
+      <c r="Z427" t="inlineStr">
         <is>
           <t>市道169号線</t>
         </is>
       </c>
-      <c r="Z427" t="inlineStr">
+      <c r="AA427" t="inlineStr">
         <is>
           <t>225</t>
         </is>
@@ -18135,16 +18125,8 @@
           <t>市道166号線</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18200,39 +18182,44 @@
       </c>
       <c r="R428" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="S428" t="inlineStr">
+      <c r="T428" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T428" t="n">
+      <c r="U428" t="n">
         <v>4000</v>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="V428" t="inlineStr">
         <is>
           <t>珠洲市正院町正院 地内</t>
         </is>
       </c>
-      <c r="V428" t="n">
+      <c r="W428" t="n">
         <v>510</v>
       </c>
-      <c r="W428" t="n">
+      <c r="X428" t="n">
         <v>7.6</v>
       </c>
-      <c r="X428" t="inlineStr">
+      <c r="Y428" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y428" t="inlineStr">
+      <c r="Z428" t="inlineStr">
         <is>
           <t>市道166号線</t>
         </is>
       </c>
-      <c r="Z428" t="inlineStr">
+      <c r="AA428" t="inlineStr">
         <is>
           <t>226</t>
         </is>
@@ -18249,16 +18236,8 @@
           <t>市道164号線</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18314,39 +18293,44 @@
       </c>
       <c r="R429" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="S429" t="inlineStr">
+      <c r="T429" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T429" t="n">
+      <c r="U429" t="n">
         <v>4014</v>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="V429" t="inlineStr">
         <is>
           <t>珠洲市正院町小路～正院 地内</t>
         </is>
       </c>
-      <c r="V429" t="n">
+      <c r="W429" t="n">
         <v>267</v>
       </c>
-      <c r="W429" t="n">
+      <c r="X429" t="n">
         <v>6.4</v>
       </c>
-      <c r="X429" t="inlineStr">
+      <c r="Y429" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y429" t="inlineStr">
+      <c r="Z429" t="inlineStr">
         <is>
           <t>市道164号線</t>
         </is>
       </c>
-      <c r="Z429" t="inlineStr">
+      <c r="AA429" t="inlineStr">
         <is>
           <t>227</t>
         </is>
@@ -18363,16 +18347,8 @@
           <t>市道179号線</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18428,39 +18404,44 @@
       </c>
       <c r="R430" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="S430" t="inlineStr">
+      <c r="T430" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T430" t="n">
+      <c r="U430" t="n">
         <v>4030</v>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="V430" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V430" t="n">
+      <c r="W430" t="n">
         <v>1994</v>
       </c>
-      <c r="W430" t="n">
+      <c r="X430" t="n">
         <v>4</v>
       </c>
-      <c r="X430" t="inlineStr">
+      <c r="Y430" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y430" t="inlineStr">
+      <c r="Z430" t="inlineStr">
         <is>
           <t>市道179号線</t>
         </is>
       </c>
-      <c r="Z430" t="inlineStr">
+      <c r="AA430" t="inlineStr">
         <is>
           <t>228</t>
         </is>
@@ -18477,16 +18458,8 @@
           <t>市道180号線</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18542,39 +18515,44 @@
       </c>
       <c r="R431" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="S431" t="inlineStr">
+      <c r="T431" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T431" t="n">
+      <c r="U431" t="n">
         <v>4030</v>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="V431" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V431" t="n">
+      <c r="W431" t="n">
         <v>1994</v>
       </c>
-      <c r="W431" t="n">
+      <c r="X431" t="n">
         <v>4</v>
       </c>
-      <c r="X431" t="inlineStr">
+      <c r="Y431" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y431" t="inlineStr">
+      <c r="Z431" t="inlineStr">
         <is>
           <t>市道180号線</t>
         </is>
       </c>
-      <c r="Z431" t="inlineStr">
+      <c r="AA431" t="inlineStr">
         <is>
           <t>229</t>
         </is>
@@ -18591,16 +18569,8 @@
           <t>市道181号線</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18656,39 +18626,44 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="S432" t="inlineStr">
+      <c r="T432" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T432" t="n">
+      <c r="U432" t="n">
         <v>4030</v>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="V432" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V432" t="n">
+      <c r="W432" t="n">
         <v>1994</v>
       </c>
-      <c r="W432" t="n">
+      <c r="X432" t="n">
         <v>4</v>
       </c>
-      <c r="X432" t="inlineStr">
+      <c r="Y432" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y432" t="inlineStr">
+      <c r="Z432" t="inlineStr">
         <is>
           <t>市道181号線</t>
         </is>
       </c>
-      <c r="Z432" t="inlineStr">
+      <c r="AA432" t="inlineStr">
         <is>
           <t>230</t>
         </is>
@@ -18705,16 +18680,8 @@
           <t>市道186号線</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18770,39 +18737,44 @@
       </c>
       <c r="R433" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="S433" t="inlineStr">
+      <c r="T433" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T433" t="n">
+      <c r="U433" t="n">
         <v>4030</v>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="V433" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V433" t="n">
+      <c r="W433" t="n">
         <v>1994</v>
       </c>
-      <c r="W433" t="n">
+      <c r="X433" t="n">
         <v>4</v>
       </c>
-      <c r="X433" t="inlineStr">
+      <c r="Y433" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y433" t="inlineStr">
+      <c r="Z433" t="inlineStr">
         <is>
           <t>市道186号線</t>
         </is>
       </c>
-      <c r="Z433" t="inlineStr">
+      <c r="AA433" t="inlineStr">
         <is>
           <t>231</t>
         </is>
@@ -18819,16 +18791,8 @@
           <t>市道701号線</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18884,39 +18848,44 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="S434" t="inlineStr">
+      <c r="T434" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T434" t="n">
+      <c r="U434" t="n">
         <v>4030</v>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="V434" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V434" t="n">
+      <c r="W434" t="n">
         <v>1994</v>
       </c>
-      <c r="W434" t="n">
+      <c r="X434" t="n">
         <v>4</v>
       </c>
-      <c r="X434" t="inlineStr">
+      <c r="Y434" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y434" t="inlineStr">
+      <c r="Z434" t="inlineStr">
         <is>
           <t>市道701号線</t>
         </is>
       </c>
-      <c r="Z434" t="inlineStr">
+      <c r="AA434" t="inlineStr">
         <is>
           <t>239</t>
         </is>
@@ -18933,16 +18902,8 @@
           <t>市道513号線</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" s="3" t="n">
         <v>46218</v>
       </c>
@@ -18998,39 +18959,44 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="S435" t="inlineStr">
+      <c r="T435" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T435" t="n">
+      <c r="U435" t="n">
         <v>4030</v>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="V435" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V435" t="n">
+      <c r="W435" t="n">
         <v>1994</v>
       </c>
-      <c r="W435" t="n">
+      <c r="X435" t="n">
         <v>4</v>
       </c>
-      <c r="X435" t="inlineStr">
+      <c r="Y435" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y435" t="inlineStr">
+      <c r="Z435" t="inlineStr">
         <is>
           <t>市道513号線</t>
         </is>
       </c>
-      <c r="Z435" t="inlineStr">
+      <c r="AA435" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -19047,16 +19013,8 @@
           <t>市道546号線</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19112,39 +19070,44 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="S436" t="inlineStr">
+      <c r="T436" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T436" t="n">
+      <c r="U436" t="n">
         <v>4030</v>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="V436" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V436" t="n">
+      <c r="W436" t="n">
         <v>1994</v>
       </c>
-      <c r="W436" t="n">
+      <c r="X436" t="n">
         <v>4</v>
       </c>
-      <c r="X436" t="inlineStr">
+      <c r="Y436" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y436" t="inlineStr">
+      <c r="Z436" t="inlineStr">
         <is>
           <t>市道546号線</t>
         </is>
       </c>
-      <c r="Z436" t="inlineStr">
+      <c r="AA436" t="inlineStr">
         <is>
           <t>238</t>
         </is>
@@ -19161,16 +19124,8 @@
           <t>市道187号線</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19226,39 +19181,44 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="S437" t="inlineStr">
+      <c r="T437" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T437" t="n">
+      <c r="U437" t="n">
         <v>4030</v>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="V437" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V437" t="n">
+      <c r="W437" t="n">
         <v>1994</v>
       </c>
-      <c r="W437" t="n">
+      <c r="X437" t="n">
         <v>4</v>
       </c>
-      <c r="X437" t="inlineStr">
+      <c r="Y437" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y437" t="inlineStr">
+      <c r="Z437" t="inlineStr">
         <is>
           <t>市道187号線</t>
         </is>
       </c>
-      <c r="Z437" t="inlineStr">
+      <c r="AA437" t="inlineStr">
         <is>
           <t>232</t>
         </is>
@@ -19275,16 +19235,8 @@
           <t>市道541号線</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr"/>
       <c r="E438" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19340,39 +19292,44 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="S438" t="inlineStr">
+      <c r="T438" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T438" t="n">
+      <c r="U438" t="n">
         <v>4030</v>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="V438" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V438" t="n">
+      <c r="W438" t="n">
         <v>1994</v>
       </c>
-      <c r="W438" t="n">
+      <c r="X438" t="n">
         <v>4</v>
       </c>
-      <c r="X438" t="inlineStr">
+      <c r="Y438" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y438" t="inlineStr">
+      <c r="Z438" t="inlineStr">
         <is>
           <t>市道541号線</t>
         </is>
       </c>
-      <c r="Z438" t="inlineStr">
+      <c r="AA438" t="inlineStr">
         <is>
           <t>237</t>
         </is>
@@ -19389,16 +19346,8 @@
           <t>市道192号線</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr"/>
       <c r="E439" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19454,39 +19403,44 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="S439" t="inlineStr">
+      <c r="T439" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T439" t="n">
+      <c r="U439" t="n">
         <v>4030</v>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="V439" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V439" t="n">
+      <c r="W439" t="n">
         <v>1994</v>
       </c>
-      <c r="W439" t="n">
+      <c r="X439" t="n">
         <v>4</v>
       </c>
-      <c r="X439" t="inlineStr">
+      <c r="Y439" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y439" t="inlineStr">
+      <c r="Z439" t="inlineStr">
         <is>
           <t>市道192号線</t>
         </is>
       </c>
-      <c r="Z439" t="inlineStr">
+      <c r="AA439" t="inlineStr">
         <is>
           <t>234</t>
         </is>
@@ -19503,16 +19457,8 @@
           <t>市道427号線</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr"/>
       <c r="E440" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19568,39 +19514,44 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="S440" t="inlineStr">
+      <c r="T440" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T440" t="n">
+      <c r="U440" t="n">
         <v>4030</v>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="V440" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V440" t="n">
+      <c r="W440" t="n">
         <v>1994</v>
       </c>
-      <c r="W440" t="n">
+      <c r="X440" t="n">
         <v>4</v>
       </c>
-      <c r="X440" t="inlineStr">
+      <c r="Y440" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y440" t="inlineStr">
+      <c r="Z440" t="inlineStr">
         <is>
           <t>市道427号線</t>
         </is>
       </c>
-      <c r="Z440" t="inlineStr">
+      <c r="AA440" t="inlineStr">
         <is>
           <t>235</t>
         </is>
@@ -19617,16 +19568,8 @@
           <t>市道189号線</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr"/>
       <c r="E441" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19682,39 +19625,44 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="S441" t="inlineStr">
+      <c r="T441" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T441" t="n">
+      <c r="U441" t="n">
         <v>4030</v>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="V441" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V441" t="n">
+      <c r="W441" t="n">
         <v>1994</v>
       </c>
-      <c r="W441" t="n">
+      <c r="X441" t="n">
         <v>4</v>
       </c>
-      <c r="X441" t="inlineStr">
+      <c r="Y441" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y441" t="inlineStr">
+      <c r="Z441" t="inlineStr">
         <is>
           <t>市道189号線</t>
         </is>
       </c>
-      <c r="Z441" t="inlineStr">
+      <c r="AA441" t="inlineStr">
         <is>
           <t>233</t>
         </is>
@@ -19731,16 +19679,8 @@
           <t>市道712号線</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19796,39 +19736,44 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="S442" t="inlineStr">
+      <c r="T442" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T442" t="n">
+      <c r="U442" t="n">
         <v>4030</v>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="V442" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V442" t="n">
+      <c r="W442" t="n">
         <v>1994</v>
       </c>
-      <c r="W442" t="n">
+      <c r="X442" t="n">
         <v>4</v>
       </c>
-      <c r="X442" t="inlineStr">
+      <c r="Y442" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y442" t="inlineStr">
+      <c r="Z442" t="inlineStr">
         <is>
           <t>市道712号線</t>
         </is>
       </c>
-      <c r="Z442" t="inlineStr">
+      <c r="AA442" t="inlineStr">
         <is>
           <t>241</t>
         </is>
@@ -19845,16 +19790,8 @@
           <t>市道711号線</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr"/>
       <c r="E443" s="3" t="n">
         <v>46218</v>
       </c>
@@ -19910,39 +19847,44 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="S443" t="inlineStr">
+      <c r="T443" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T443" t="n">
+      <c r="U443" t="n">
         <v>4030</v>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="V443" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V443" t="n">
+      <c r="W443" t="n">
         <v>1994</v>
       </c>
-      <c r="W443" t="n">
+      <c r="X443" t="n">
         <v>4</v>
       </c>
-      <c r="X443" t="inlineStr">
+      <c r="Y443" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y443" t="inlineStr">
+      <c r="Z443" t="inlineStr">
         <is>
           <t>市道711号線</t>
         </is>
       </c>
-      <c r="Z443" t="inlineStr">
+      <c r="AA443" t="inlineStr">
         <is>
           <t>240</t>
         </is>
@@ -19959,16 +19901,8 @@
           <t>市道32号線</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr"/>
       <c r="E444" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20024,39 +19958,44 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="S444" t="inlineStr">
+      <c r="T444" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T444" t="n">
+      <c r="U444" t="n">
         <v>4092</v>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="V444" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V444" t="n">
+      <c r="W444" t="n">
         <v>1859</v>
       </c>
-      <c r="W444" t="n">
+      <c r="X444" t="n">
         <v>3.5</v>
       </c>
-      <c r="X444" t="inlineStr">
+      <c r="Y444" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y444" t="inlineStr">
+      <c r="Z444" t="inlineStr">
         <is>
           <t>市道32号線</t>
         </is>
       </c>
-      <c r="Z444" t="inlineStr">
+      <c r="AA444" t="inlineStr">
         <is>
           <t>246</t>
         </is>
@@ -20073,16 +20012,8 @@
           <t>市道182号線</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
       <c r="E445" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20138,39 +20069,44 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="S445" t="inlineStr">
+      <c r="T445" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T445" t="n">
+      <c r="U445" t="n">
         <v>4092</v>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="V445" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V445" t="n">
+      <c r="W445" t="n">
         <v>1859</v>
       </c>
-      <c r="W445" t="n">
+      <c r="X445" t="n">
         <v>3.5</v>
       </c>
-      <c r="X445" t="inlineStr">
+      <c r="Y445" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y445" t="inlineStr">
+      <c r="Z445" t="inlineStr">
         <is>
           <t>市道182号線</t>
         </is>
       </c>
-      <c r="Z445" t="inlineStr">
+      <c r="AA445" t="inlineStr">
         <is>
           <t>242</t>
         </is>
@@ -20187,16 +20123,8 @@
           <t>市道184号線</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20252,39 +20180,44 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="S446" t="inlineStr">
+      <c r="T446" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T446" t="n">
+      <c r="U446" t="n">
         <v>4092</v>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="V446" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V446" t="n">
+      <c r="W446" t="n">
         <v>1859</v>
       </c>
-      <c r="W446" t="n">
+      <c r="X446" t="n">
         <v>3.5</v>
       </c>
-      <c r="X446" t="inlineStr">
+      <c r="Y446" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y446" t="inlineStr">
+      <c r="Z446" t="inlineStr">
         <is>
           <t>市道184号線</t>
         </is>
       </c>
-      <c r="Z446" t="inlineStr">
+      <c r="AA446" t="inlineStr">
         <is>
           <t>243</t>
         </is>
@@ -20301,16 +20234,8 @@
           <t>市道188号線</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20366,39 +20291,44 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="S447" t="inlineStr">
+      <c r="T447" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T447" t="n">
+      <c r="U447" t="n">
         <v>4092</v>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="V447" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V447" t="n">
+      <c r="W447" t="n">
         <v>1859</v>
       </c>
-      <c r="W447" t="n">
+      <c r="X447" t="n">
         <v>3.5</v>
       </c>
-      <c r="X447" t="inlineStr">
+      <c r="Y447" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y447" t="inlineStr">
+      <c r="Z447" t="inlineStr">
         <is>
           <t>市道188号線</t>
         </is>
       </c>
-      <c r="Z447" t="inlineStr">
+      <c r="AA447" t="inlineStr">
         <is>
           <t>244</t>
         </is>
@@ -20415,16 +20345,8 @@
           <t>市道190号線</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20480,39 +20402,44 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="S448" t="inlineStr">
+      <c r="T448" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T448" t="n">
+      <c r="U448" t="n">
         <v>4092</v>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="V448" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V448" t="n">
+      <c r="W448" t="n">
         <v>1859</v>
       </c>
-      <c r="W448" t="n">
+      <c r="X448" t="n">
         <v>3.5</v>
       </c>
-      <c r="X448" t="inlineStr">
+      <c r="Y448" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y448" t="inlineStr">
+      <c r="Z448" t="inlineStr">
         <is>
           <t>市道190号線</t>
         </is>
       </c>
-      <c r="Z448" t="inlineStr">
+      <c r="AA448" t="inlineStr">
         <is>
           <t>245</t>
         </is>
@@ -20529,16 +20456,8 @@
           <t>市道416号線</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20594,39 +20513,44 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="S449" t="inlineStr">
+      <c r="T449" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T449" t="n">
+      <c r="U449" t="n">
         <v>4092</v>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="V449" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V449" t="n">
+      <c r="W449" t="n">
         <v>1859</v>
       </c>
-      <c r="W449" t="n">
+      <c r="X449" t="n">
         <v>3.5</v>
       </c>
-      <c r="X449" t="inlineStr">
+      <c r="Y449" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y449" t="inlineStr">
+      <c r="Z449" t="inlineStr">
         <is>
           <t>市道416号線</t>
         </is>
       </c>
-      <c r="Z449" t="inlineStr">
+      <c r="AA449" t="inlineStr">
         <is>
           <t>247</t>
         </is>
@@ -20643,16 +20567,8 @@
           <t>市道453号線</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20708,39 +20624,44 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="S450" t="inlineStr">
+      <c r="T450" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T450" t="n">
+      <c r="U450" t="n">
         <v>4092</v>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="V450" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V450" t="n">
+      <c r="W450" t="n">
         <v>1859</v>
       </c>
-      <c r="W450" t="n">
+      <c r="X450" t="n">
         <v>3.5</v>
       </c>
-      <c r="X450" t="inlineStr">
+      <c r="Y450" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y450" t="inlineStr">
+      <c r="Z450" t="inlineStr">
         <is>
           <t>市道453号線</t>
         </is>
       </c>
-      <c r="Z450" t="inlineStr">
+      <c r="AA450" t="inlineStr">
         <is>
           <t>248</t>
         </is>
@@ -20757,16 +20678,8 @@
           <t>市道569号線</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20822,39 +20735,44 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="S451" t="inlineStr">
+      <c r="T451" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T451" t="n">
+      <c r="U451" t="n">
         <v>4092</v>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="V451" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内</t>
         </is>
       </c>
-      <c r="V451" t="n">
+      <c r="W451" t="n">
         <v>1859</v>
       </c>
-      <c r="W451" t="n">
+      <c r="X451" t="n">
         <v>3.5</v>
       </c>
-      <c r="X451" t="inlineStr">
+      <c r="Y451" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y451" t="inlineStr">
+      <c r="Z451" t="inlineStr">
         <is>
           <t>市道569号線</t>
         </is>
       </c>
-      <c r="Z451" t="inlineStr">
+      <c r="AA451" t="inlineStr">
         <is>
           <t>249</t>
         </is>
@@ -20871,16 +20789,8 @@
           <t>市道462号線</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" s="3" t="n">
         <v>46218</v>
       </c>
@@ -20936,39 +20846,44 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="S452" t="inlineStr">
+      <c r="T452" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T452" t="n">
+      <c r="U452" t="n">
         <v>4159</v>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="V452" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V452" t="n">
+      <c r="W452" t="n">
         <v>2774</v>
       </c>
-      <c r="W452" t="n">
+      <c r="X452" t="n">
         <v>4.5</v>
       </c>
-      <c r="X452" t="inlineStr">
+      <c r="Y452" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y452" t="inlineStr">
+      <c r="Z452" t="inlineStr">
         <is>
           <t>市道462号線</t>
         </is>
       </c>
-      <c r="Z452" t="inlineStr">
+      <c r="AA452" t="inlineStr">
         <is>
           <t>260</t>
         </is>
@@ -20985,16 +20900,8 @@
           <t>市道170号線</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21050,39 +20957,44 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="S453" t="inlineStr">
+      <c r="T453" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T453" t="n">
+      <c r="U453" t="n">
         <v>4159</v>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="V453" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V453" t="n">
+      <c r="W453" t="n">
         <v>2774</v>
       </c>
-      <c r="W453" t="n">
+      <c r="X453" t="n">
         <v>4.5</v>
       </c>
-      <c r="X453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y453" t="inlineStr">
+      <c r="Z453" t="inlineStr">
         <is>
           <t>市道170号線</t>
         </is>
       </c>
-      <c r="Z453" t="inlineStr">
+      <c r="AA453" t="inlineStr">
         <is>
           <t>254</t>
         </is>
@@ -21099,16 +21011,8 @@
           <t>市道172号線</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21164,39 +21068,44 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="S454" t="inlineStr">
+      <c r="T454" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T454" t="n">
+      <c r="U454" t="n">
         <v>4159</v>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="V454" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V454" t="n">
+      <c r="W454" t="n">
         <v>2774</v>
       </c>
-      <c r="W454" t="n">
+      <c r="X454" t="n">
         <v>4.5</v>
       </c>
-      <c r="X454" t="inlineStr">
+      <c r="Y454" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y454" t="inlineStr">
+      <c r="Z454" t="inlineStr">
         <is>
           <t>市道172号線</t>
         </is>
       </c>
-      <c r="Z454" t="inlineStr">
+      <c r="AA454" t="inlineStr">
         <is>
           <t>255</t>
         </is>
@@ -21213,16 +21122,8 @@
           <t>市道165号線</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21278,39 +21179,44 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="S455" t="inlineStr">
+      <c r="T455" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T455" t="n">
+      <c r="U455" t="n">
         <v>4159</v>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="V455" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V455" t="n">
+      <c r="W455" t="n">
         <v>2774</v>
       </c>
-      <c r="W455" t="n">
+      <c r="X455" t="n">
         <v>4.5</v>
       </c>
-      <c r="X455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y455" t="inlineStr">
+      <c r="Z455" t="inlineStr">
         <is>
           <t>市道165号線</t>
         </is>
       </c>
-      <c r="Z455" t="inlineStr">
+      <c r="AA455" t="inlineStr">
         <is>
           <t>253</t>
         </is>
@@ -21327,16 +21233,8 @@
           <t>市道573号線</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21392,39 +21290,44 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="S456" t="inlineStr">
+      <c r="T456" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T456" t="n">
+      <c r="U456" t="n">
         <v>4159</v>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="V456" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V456" t="n">
+      <c r="W456" t="n">
         <v>2774</v>
       </c>
-      <c r="W456" t="n">
+      <c r="X456" t="n">
         <v>4.5</v>
       </c>
-      <c r="X456" t="inlineStr">
+      <c r="Y456" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y456" t="inlineStr">
+      <c r="Z456" t="inlineStr">
         <is>
           <t>市道573号線</t>
         </is>
       </c>
-      <c r="Z456" t="inlineStr">
+      <c r="AA456" t="inlineStr">
         <is>
           <t>262</t>
         </is>
@@ -21441,16 +21344,8 @@
           <t>市道175号線</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21506,39 +21401,44 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="S457" t="inlineStr">
+      <c r="T457" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T457" t="n">
+      <c r="U457" t="n">
         <v>4159</v>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="V457" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V457" t="n">
+      <c r="W457" t="n">
         <v>2774</v>
       </c>
-      <c r="W457" t="n">
+      <c r="X457" t="n">
         <v>4.5</v>
       </c>
-      <c r="X457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y457" t="inlineStr">
+      <c r="Z457" t="inlineStr">
         <is>
           <t>市道175号線</t>
         </is>
       </c>
-      <c r="Z457" t="inlineStr">
+      <c r="AA457" t="inlineStr">
         <is>
           <t>256</t>
         </is>
@@ -21555,16 +21455,8 @@
           <t>市道440号線</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21620,39 +21512,44 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="S458" t="inlineStr">
+      <c r="T458" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T458" t="n">
+      <c r="U458" t="n">
         <v>4159</v>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="V458" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V458" t="n">
+      <c r="W458" t="n">
         <v>2774</v>
       </c>
-      <c r="W458" t="n">
+      <c r="X458" t="n">
         <v>4.5</v>
       </c>
-      <c r="X458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y458" t="inlineStr">
+      <c r="Z458" t="inlineStr">
         <is>
           <t>市道440号線</t>
         </is>
       </c>
-      <c r="Z458" t="inlineStr">
+      <c r="AA458" t="inlineStr">
         <is>
           <t>259</t>
         </is>
@@ -21669,16 +21566,8 @@
           <t>市道176号線</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21734,39 +21623,44 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="S459" t="inlineStr">
+      <c r="T459" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T459" t="n">
+      <c r="U459" t="n">
         <v>4159</v>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="V459" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V459" t="n">
+      <c r="W459" t="n">
         <v>2774</v>
       </c>
-      <c r="W459" t="n">
+      <c r="X459" t="n">
         <v>4.5</v>
       </c>
-      <c r="X459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y459" t="inlineStr">
+      <c r="Z459" t="inlineStr">
         <is>
           <t>市道176号線</t>
         </is>
       </c>
-      <c r="Z459" t="inlineStr">
+      <c r="AA459" t="inlineStr">
         <is>
           <t>257</t>
         </is>
@@ -21783,16 +21677,8 @@
           <t>市道525号線</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr"/>
       <c r="E460" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21848,39 +21734,44 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="S460" t="inlineStr">
+      <c r="T460" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T460" t="n">
+      <c r="U460" t="n">
         <v>4159</v>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="V460" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V460" t="n">
+      <c r="W460" t="n">
         <v>2774</v>
       </c>
-      <c r="W460" t="n">
+      <c r="X460" t="n">
         <v>4.5</v>
       </c>
-      <c r="X460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y460" t="inlineStr">
+      <c r="Z460" t="inlineStr">
         <is>
           <t>市道525号線</t>
         </is>
       </c>
-      <c r="Z460" t="inlineStr">
+      <c r="AA460" t="inlineStr">
         <is>
           <t>261</t>
         </is>
@@ -21897,16 +21788,8 @@
           <t>市道673号線</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" s="3" t="n">
         <v>46218</v>
       </c>
@@ -21962,39 +21845,44 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="S461" t="inlineStr">
+      <c r="T461" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T461" t="n">
+      <c r="U461" t="n">
         <v>4159</v>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="V461" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V461" t="n">
+      <c r="W461" t="n">
         <v>2774</v>
       </c>
-      <c r="W461" t="n">
+      <c r="X461" t="n">
         <v>4.5</v>
       </c>
-      <c r="X461" t="inlineStr">
+      <c r="Y461" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y461" t="inlineStr">
+      <c r="Z461" t="inlineStr">
         <is>
           <t>市道673号線</t>
         </is>
       </c>
-      <c r="Z461" t="inlineStr">
+      <c r="AA461" t="inlineStr">
         <is>
           <t>263</t>
         </is>
@@ -22011,16 +21899,8 @@
           <t>市道177号線</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr"/>
       <c r="E462" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22076,39 +21956,44 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="S462" t="inlineStr">
+      <c r="T462" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T462" t="n">
+      <c r="U462" t="n">
         <v>4159</v>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="V462" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V462" t="n">
+      <c r="W462" t="n">
         <v>2774</v>
       </c>
-      <c r="W462" t="n">
+      <c r="X462" t="n">
         <v>4.5</v>
       </c>
-      <c r="X462" t="inlineStr">
+      <c r="Y462" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y462" t="inlineStr">
+      <c r="Z462" t="inlineStr">
         <is>
           <t>市道177号線</t>
         </is>
       </c>
-      <c r="Z462" t="inlineStr">
+      <c r="AA462" t="inlineStr">
         <is>
           <t>258</t>
         </is>
@@ -22125,16 +22010,8 @@
           <t>市道156号線</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22190,39 +22067,44 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="S463" t="inlineStr">
+      <c r="T463" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T463" t="n">
+      <c r="U463" t="n">
         <v>4159</v>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="V463" t="inlineStr">
         <is>
           <t>珠洲市正院町 地内外</t>
         </is>
       </c>
-      <c r="V463" t="n">
+      <c r="W463" t="n">
         <v>2774</v>
       </c>
-      <c r="W463" t="n">
+      <c r="X463" t="n">
         <v>4.5</v>
       </c>
-      <c r="X463" t="inlineStr">
+      <c r="Y463" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y463" t="inlineStr">
+      <c r="Z463" t="inlineStr">
         <is>
           <t>市道156号線</t>
         </is>
       </c>
-      <c r="Z463" t="inlineStr">
+      <c r="AA463" t="inlineStr">
         <is>
           <t>250</t>
         </is>
@@ -22239,16 +22121,8 @@
           <t>市道740号線</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr"/>
       <c r="E464" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22304,39 +22178,44 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S464" t="inlineStr">
+      <c r="T464" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T464" t="n">
+      <c r="U464" t="n">
         <v>3987</v>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="V464" t="inlineStr">
         <is>
           <t>珠洲市宝立町金峰寺～上戸町北方 地内</t>
         </is>
       </c>
-      <c r="V464" t="n">
+      <c r="W464" t="n">
         <v>4951</v>
       </c>
-      <c r="W464" t="n">
+      <c r="X464" t="n">
         <v>10.4</v>
       </c>
-      <c r="X464" t="inlineStr">
+      <c r="Y464" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y464" t="inlineStr">
+      <c r="Z464" t="inlineStr">
         <is>
           <t>市道740号線</t>
         </is>
       </c>
-      <c r="Z464" t="inlineStr">
+      <c r="AA464" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -22353,16 +22232,8 @@
           <t>市道70号線</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr"/>
       <c r="E465" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22418,39 +22289,44 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S465" t="inlineStr">
+      <c r="T465" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T465" t="n">
+      <c r="U465" t="n">
         <v>3948</v>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="V465" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼 地内</t>
         </is>
       </c>
-      <c r="V465" t="n">
+      <c r="W465" t="n">
         <v>590</v>
       </c>
-      <c r="W465" t="n">
+      <c r="X465" t="n">
         <v>6.4</v>
       </c>
-      <c r="X465" t="inlineStr">
+      <c r="Y465" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y465" t="inlineStr">
+      <c r="Z465" t="inlineStr">
         <is>
           <t>市道70号線</t>
         </is>
       </c>
-      <c r="Z465" t="inlineStr">
+      <c r="AA465" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -22467,16 +22343,8 @@
           <t>市道72号線</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr"/>
       <c r="E466" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22532,39 +22400,44 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S466" t="inlineStr">
+      <c r="T466" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T466" t="n">
+      <c r="U466" t="n">
         <v>3949</v>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="V466" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼～春日野 地内</t>
         </is>
       </c>
-      <c r="V466" t="n">
+      <c r="W466" t="n">
         <v>1972</v>
       </c>
-      <c r="W466" t="n">
+      <c r="X466" t="n">
         <v>3.9</v>
       </c>
-      <c r="X466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y466" t="inlineStr">
+      <c r="Z466" t="inlineStr">
         <is>
           <t>市道72号線</t>
         </is>
       </c>
-      <c r="Z466" t="inlineStr">
+      <c r="AA466" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -22581,16 +22454,8 @@
           <t>市道438号線</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr"/>
       <c r="E467" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22646,39 +22511,44 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S467" t="inlineStr">
+      <c r="T467" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T467" t="n">
+      <c r="U467" t="n">
         <v>3950</v>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="V467" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜飼 地内</t>
         </is>
       </c>
-      <c r="V467" t="n">
+      <c r="W467" t="n">
         <v>688</v>
       </c>
-      <c r="W467" t="n">
+      <c r="X467" t="n">
         <v>6.1</v>
       </c>
-      <c r="X467" t="inlineStr">
+      <c r="Y467" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y467" t="inlineStr">
+      <c r="Z467" t="inlineStr">
         <is>
           <t>市道438号線</t>
         </is>
       </c>
-      <c r="Z467" t="inlineStr">
+      <c r="AA467" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -22695,16 +22565,8 @@
           <t>市道556号線</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr"/>
       <c r="E468" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22760,39 +22622,44 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S468" t="inlineStr">
+      <c r="T468" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T468" t="n">
+      <c r="U468" t="n">
         <v>3969</v>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="V468" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜島 地内</t>
         </is>
       </c>
-      <c r="V468" t="n">
+      <c r="W468" t="n">
         <v>331</v>
       </c>
-      <c r="W468" t="n">
+      <c r="X468" t="n">
         <v>15.4</v>
       </c>
-      <c r="X468" t="inlineStr">
+      <c r="Y468" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y468" t="inlineStr">
+      <c r="Z468" t="inlineStr">
         <is>
           <t>市道556号線</t>
         </is>
       </c>
-      <c r="Z468" t="inlineStr">
+      <c r="AA468" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -22809,16 +22676,8 @@
           <t>市道340号線</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
       <c r="E469" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22874,39 +22733,44 @@
       </c>
       <c r="R469" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S469" t="inlineStr">
+      <c r="T469" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T469" t="n">
+      <c r="U469" t="n">
         <v>4063</v>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="V469" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V469" t="n">
+      <c r="W469" t="n">
         <v>5081</v>
       </c>
-      <c r="W469" t="n">
+      <c r="X469" t="n">
         <v>3.9</v>
       </c>
-      <c r="X469" t="inlineStr">
+      <c r="Y469" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y469" t="inlineStr">
+      <c r="Z469" t="inlineStr">
         <is>
           <t>市道340号線</t>
         </is>
       </c>
-      <c r="Z469" t="inlineStr">
+      <c r="AA469" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -22923,16 +22787,8 @@
           <t>市道680号線</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr"/>
       <c r="E470" s="3" t="n">
         <v>46218</v>
       </c>
@@ -22988,39 +22844,44 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="S470" t="inlineStr">
+      <c r="T470" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T470" t="n">
+      <c r="U470" t="n">
         <v>4063</v>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="V470" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V470" t="n">
+      <c r="W470" t="n">
         <v>5081</v>
       </c>
-      <c r="W470" t="n">
+      <c r="X470" t="n">
         <v>3.9</v>
       </c>
-      <c r="X470" t="inlineStr">
+      <c r="Y470" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y470" t="inlineStr">
+      <c r="Z470" t="inlineStr">
         <is>
           <t>市道680号線</t>
         </is>
       </c>
-      <c r="Z470" t="inlineStr">
+      <c r="AA470" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -23037,16 +22898,8 @@
           <t>市道583号線</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr"/>
       <c r="E471" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23102,39 +22955,44 @@
       </c>
       <c r="R471" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="S471" t="inlineStr">
+      <c r="T471" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T471" t="n">
+      <c r="U471" t="n">
         <v>4063</v>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="V471" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V471" t="n">
+      <c r="W471" t="n">
         <v>5081</v>
       </c>
-      <c r="W471" t="n">
+      <c r="X471" t="n">
         <v>3.9</v>
       </c>
-      <c r="X471" t="inlineStr">
+      <c r="Y471" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y471" t="inlineStr">
+      <c r="Z471" t="inlineStr">
         <is>
           <t>市道583号線</t>
         </is>
       </c>
-      <c r="Z471" t="inlineStr">
+      <c r="AA471" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -23151,16 +23009,8 @@
           <t>市道666号線</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23216,39 +23066,44 @@
       </c>
       <c r="R472" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="S472" t="inlineStr">
+      <c r="T472" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T472" t="n">
+      <c r="U472" t="n">
         <v>4063</v>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="V472" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V472" t="n">
+      <c r="W472" t="n">
         <v>5081</v>
       </c>
-      <c r="W472" t="n">
+      <c r="X472" t="n">
         <v>3.9</v>
       </c>
-      <c r="X472" t="inlineStr">
+      <c r="Y472" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y472" t="inlineStr">
+      <c r="Z472" t="inlineStr">
         <is>
           <t>市道666号線</t>
         </is>
       </c>
-      <c r="Z472" t="inlineStr">
+      <c r="AA472" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -23265,16 +23120,8 @@
           <t>市道390号線</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23330,39 +23177,44 @@
       </c>
       <c r="R473" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S473" t="inlineStr">
+      <c r="T473" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T473" t="n">
+      <c r="U473" t="n">
         <v>4063</v>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="V473" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V473" t="n">
+      <c r="W473" t="n">
         <v>5081</v>
       </c>
-      <c r="W473" t="n">
+      <c r="X473" t="n">
         <v>3.9</v>
       </c>
-      <c r="X473" t="inlineStr">
+      <c r="Y473" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y473" t="inlineStr">
+      <c r="Z473" t="inlineStr">
         <is>
           <t>市道390号線</t>
         </is>
       </c>
-      <c r="Z473" t="inlineStr">
+      <c r="AA473" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -23379,16 +23231,8 @@
           <t>市道717号線</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23444,39 +23288,44 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="S474" t="inlineStr">
+      <c r="T474" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T474" t="n">
+      <c r="U474" t="n">
         <v>4063</v>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="V474" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V474" t="n">
+      <c r="W474" t="n">
         <v>5081</v>
       </c>
-      <c r="W474" t="n">
+      <c r="X474" t="n">
         <v>3.9</v>
       </c>
-      <c r="X474" t="inlineStr">
+      <c r="Y474" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y474" t="inlineStr">
+      <c r="Z474" t="inlineStr">
         <is>
           <t>市道717号線</t>
         </is>
       </c>
-      <c r="Z474" t="inlineStr">
+      <c r="AA474" t="inlineStr">
         <is>
           <t>64</t>
         </is>
@@ -23493,16 +23342,8 @@
           <t>市道394号線</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23558,39 +23399,44 @@
       </c>
       <c r="R475" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S475" t="inlineStr">
+      <c r="T475" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T475" t="n">
+      <c r="U475" t="n">
         <v>4063</v>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="V475" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V475" t="n">
+      <c r="W475" t="n">
         <v>5081</v>
       </c>
-      <c r="W475" t="n">
+      <c r="X475" t="n">
         <v>3.9</v>
       </c>
-      <c r="X475" t="inlineStr">
+      <c r="Y475" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y475" t="inlineStr">
+      <c r="Z475" t="inlineStr">
         <is>
           <t>市道394号線</t>
         </is>
       </c>
-      <c r="Z475" t="inlineStr">
+      <c r="AA475" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -23607,16 +23453,8 @@
           <t>市道716号線</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23672,39 +23510,44 @@
       </c>
       <c r="R476" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="S476" t="inlineStr">
+      <c r="T476" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T476" t="n">
+      <c r="U476" t="n">
         <v>4063</v>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="V476" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V476" t="n">
+      <c r="W476" t="n">
         <v>5081</v>
       </c>
-      <c r="W476" t="n">
+      <c r="X476" t="n">
         <v>3.9</v>
       </c>
-      <c r="X476" t="inlineStr">
+      <c r="Y476" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y476" t="inlineStr">
+      <c r="Z476" t="inlineStr">
         <is>
           <t>市道716号線</t>
         </is>
       </c>
-      <c r="Z476" t="inlineStr">
+      <c r="AA476" t="inlineStr">
         <is>
           <t>63</t>
         </is>
@@ -23721,16 +23564,8 @@
           <t>市道392号線</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23786,39 +23621,44 @@
       </c>
       <c r="R477" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="S477" t="inlineStr">
+      <c r="T477" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T477" t="n">
+      <c r="U477" t="n">
         <v>4063</v>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="V477" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V477" t="n">
+      <c r="W477" t="n">
         <v>5081</v>
       </c>
-      <c r="W477" t="n">
+      <c r="X477" t="n">
         <v>3.9</v>
       </c>
-      <c r="X477" t="inlineStr">
+      <c r="Y477" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y477" t="inlineStr">
+      <c r="Z477" t="inlineStr">
         <is>
           <t>市道392号線</t>
         </is>
       </c>
-      <c r="Z477" t="inlineStr">
+      <c r="AA477" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -23835,16 +23675,8 @@
           <t>市道358号線</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" s="3" t="n">
         <v>46218</v>
       </c>
@@ -23900,39 +23732,44 @@
       </c>
       <c r="R478" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S478" t="inlineStr">
+      <c r="T478" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T478" t="n">
+      <c r="U478" t="n">
         <v>4063</v>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="V478" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V478" t="n">
+      <c r="W478" t="n">
         <v>5081</v>
       </c>
-      <c r="W478" t="n">
+      <c r="X478" t="n">
         <v>3.9</v>
       </c>
-      <c r="X478" t="inlineStr">
+      <c r="Y478" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y478" t="inlineStr">
+      <c r="Z478" t="inlineStr">
         <is>
           <t>市道358号線</t>
         </is>
       </c>
-      <c r="Z478" t="inlineStr">
+      <c r="AA478" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -23949,16 +23786,8 @@
           <t>市道422号線</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24014,39 +23843,44 @@
       </c>
       <c r="R479" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="S479" t="inlineStr">
+      <c r="T479" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T479" t="n">
+      <c r="U479" t="n">
         <v>4063</v>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="V479" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V479" t="n">
+      <c r="W479" t="n">
         <v>5081</v>
       </c>
-      <c r="W479" t="n">
+      <c r="X479" t="n">
         <v>3.9</v>
       </c>
-      <c r="X479" t="inlineStr">
+      <c r="Y479" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y479" t="inlineStr">
+      <c r="Z479" t="inlineStr">
         <is>
           <t>市道422号線</t>
         </is>
       </c>
-      <c r="Z479" t="inlineStr">
+      <c r="AA479" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -24063,16 +23897,8 @@
           <t>市道660号線</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24128,39 +23954,44 @@
       </c>
       <c r="R480" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="S480" t="inlineStr">
+      <c r="T480" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T480" t="n">
+      <c r="U480" t="n">
         <v>4063</v>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="V480" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V480" t="n">
+      <c r="W480" t="n">
         <v>5081</v>
       </c>
-      <c r="W480" t="n">
+      <c r="X480" t="n">
         <v>3.9</v>
       </c>
-      <c r="X480" t="inlineStr">
+      <c r="Y480" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y480" t="inlineStr">
+      <c r="Z480" t="inlineStr">
         <is>
           <t>市道660号線</t>
         </is>
       </c>
-      <c r="Z480" t="inlineStr">
+      <c r="AA480" t="inlineStr">
         <is>
           <t>57</t>
         </is>
@@ -24177,16 +24008,8 @@
           <t>市道510号線</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24242,39 +24065,44 @@
       </c>
       <c r="R481" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S481" t="inlineStr">
+      <c r="T481" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T481" t="n">
+      <c r="U481" t="n">
         <v>4063</v>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="V481" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V481" t="n">
+      <c r="W481" t="n">
         <v>5081</v>
       </c>
-      <c r="W481" t="n">
+      <c r="X481" t="n">
         <v>3.9</v>
       </c>
-      <c r="X481" t="inlineStr">
+      <c r="Y481" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y481" t="inlineStr">
+      <c r="Z481" t="inlineStr">
         <is>
           <t>市道510号線</t>
         </is>
       </c>
-      <c r="Z481" t="inlineStr">
+      <c r="AA481" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -24291,16 +24119,8 @@
           <t>市道354号線</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr"/>
       <c r="E482" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24356,39 +24176,44 @@
       </c>
       <c r="R482" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S482" t="inlineStr">
+      <c r="T482" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T482" t="n">
+      <c r="U482" t="n">
         <v>4063</v>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="V482" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V482" t="n">
+      <c r="W482" t="n">
         <v>5081</v>
       </c>
-      <c r="W482" t="n">
+      <c r="X482" t="n">
         <v>3.9</v>
       </c>
-      <c r="X482" t="inlineStr">
+      <c r="Y482" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y482" t="inlineStr">
+      <c r="Z482" t="inlineStr">
         <is>
           <t>市道354号線</t>
         </is>
       </c>
-      <c r="Z482" t="inlineStr">
+      <c r="AA482" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -24405,16 +24230,8 @@
           <t>市道417号線</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr"/>
       <c r="E483" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24470,39 +24287,44 @@
       </c>
       <c r="R483" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S483" t="inlineStr">
+      <c r="T483" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T483" t="n">
+      <c r="U483" t="n">
         <v>4063</v>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="V483" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V483" t="n">
+      <c r="W483" t="n">
         <v>5081</v>
       </c>
-      <c r="W483" t="n">
+      <c r="X483" t="n">
         <v>3.9</v>
       </c>
-      <c r="X483" t="inlineStr">
+      <c r="Y483" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y483" t="inlineStr">
+      <c r="Z483" t="inlineStr">
         <is>
           <t>市道417号線</t>
         </is>
       </c>
-      <c r="Z483" t="inlineStr">
+      <c r="AA483" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -24519,16 +24341,8 @@
           <t>市道418号線</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr"/>
       <c r="E484" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24584,39 +24398,44 @@
       </c>
       <c r="R484" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S484" t="inlineStr">
+      <c r="T484" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T484" t="n">
+      <c r="U484" t="n">
         <v>4063</v>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="V484" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V484" t="n">
+      <c r="W484" t="n">
         <v>5081</v>
       </c>
-      <c r="W484" t="n">
+      <c r="X484" t="n">
         <v>3.9</v>
       </c>
-      <c r="X484" t="inlineStr">
+      <c r="Y484" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y484" t="inlineStr">
+      <c r="Z484" t="inlineStr">
         <is>
           <t>市道418号線</t>
         </is>
       </c>
-      <c r="Z484" t="inlineStr">
+      <c r="AA484" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -24633,16 +24452,8 @@
           <t>市道355号線</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
       <c r="E485" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24698,39 +24509,44 @@
       </c>
       <c r="R485" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S485" t="inlineStr">
+      <c r="T485" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T485" t="n">
+      <c r="U485" t="n">
         <v>4063</v>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="V485" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V485" t="n">
+      <c r="W485" t="n">
         <v>5081</v>
       </c>
-      <c r="W485" t="n">
+      <c r="X485" t="n">
         <v>3.9</v>
       </c>
-      <c r="X485" t="inlineStr">
+      <c r="Y485" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y485" t="inlineStr">
+      <c r="Z485" t="inlineStr">
         <is>
           <t>市道355号線</t>
         </is>
       </c>
-      <c r="Z485" t="inlineStr">
+      <c r="AA485" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -24747,16 +24563,8 @@
           <t>市道604号線</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
       <c r="E486" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24812,39 +24620,44 @@
       </c>
       <c r="R486" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="S486" t="inlineStr">
+      <c r="T486" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T486" t="n">
+      <c r="U486" t="n">
         <v>4063</v>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="V486" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V486" t="n">
+      <c r="W486" t="n">
         <v>5081</v>
       </c>
-      <c r="W486" t="n">
+      <c r="X486" t="n">
         <v>3.9</v>
       </c>
-      <c r="X486" t="inlineStr">
+      <c r="Y486" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y486" t="inlineStr">
+      <c r="Z486" t="inlineStr">
         <is>
           <t>市道604号線</t>
         </is>
       </c>
-      <c r="Z486" t="inlineStr">
+      <c r="AA486" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -24861,16 +24674,8 @@
           <t>市道84号線</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr"/>
       <c r="E487" s="3" t="n">
         <v>46218</v>
       </c>
@@ -24926,39 +24731,44 @@
       </c>
       <c r="R487" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="S487" t="inlineStr">
+      <c r="T487" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T487" t="n">
+      <c r="U487" t="n">
         <v>4063</v>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="V487" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V487" t="n">
+      <c r="W487" t="n">
         <v>5081</v>
       </c>
-      <c r="W487" t="n">
+      <c r="X487" t="n">
         <v>3.9</v>
       </c>
-      <c r="X487" t="inlineStr">
+      <c r="Y487" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y487" t="inlineStr">
+      <c r="Z487" t="inlineStr">
         <is>
           <t>市道84号線</t>
         </is>
       </c>
-      <c r="Z487" t="inlineStr">
+      <c r="AA487" t="inlineStr">
         <is>
           <t>65</t>
         </is>
@@ -24975,16 +24785,8 @@
           <t>市道433号線</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25040,39 +24842,44 @@
       </c>
       <c r="R488" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="S488" t="inlineStr">
+      <c r="T488" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T488" t="n">
+      <c r="U488" t="n">
         <v>4063</v>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="V488" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V488" t="n">
+      <c r="W488" t="n">
         <v>5081</v>
       </c>
-      <c r="W488" t="n">
+      <c r="X488" t="n">
         <v>3.9</v>
       </c>
-      <c r="X488" t="inlineStr">
+      <c r="Y488" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y488" t="inlineStr">
+      <c r="Z488" t="inlineStr">
         <is>
           <t>市道433号線</t>
         </is>
       </c>
-      <c r="Z488" t="inlineStr">
+      <c r="AA488" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -25089,16 +24896,8 @@
           <t>市道473号線</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25154,39 +24953,44 @@
       </c>
       <c r="R489" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="S489" t="inlineStr">
+      <c r="T489" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T489" t="n">
+      <c r="U489" t="n">
         <v>4063</v>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="V489" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V489" t="n">
+      <c r="W489" t="n">
         <v>5081</v>
       </c>
-      <c r="W489" t="n">
+      <c r="X489" t="n">
         <v>3.9</v>
       </c>
-      <c r="X489" t="inlineStr">
+      <c r="Y489" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y489" t="inlineStr">
+      <c r="Z489" t="inlineStr">
         <is>
           <t>市道473号線</t>
         </is>
       </c>
-      <c r="Z489" t="inlineStr">
+      <c r="AA489" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -25203,16 +25007,8 @@
           <t>市道472号線</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25268,39 +25064,44 @@
       </c>
       <c r="R490" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="S490" t="inlineStr">
+      <c r="T490" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T490" t="n">
+      <c r="U490" t="n">
         <v>4063</v>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="V490" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V490" t="n">
+      <c r="W490" t="n">
         <v>5081</v>
       </c>
-      <c r="W490" t="n">
+      <c r="X490" t="n">
         <v>3.9</v>
       </c>
-      <c r="X490" t="inlineStr">
+      <c r="Y490" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y490" t="inlineStr">
+      <c r="Z490" t="inlineStr">
         <is>
           <t>市道472号線</t>
         </is>
       </c>
-      <c r="Z490" t="inlineStr">
+      <c r="AA490" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -25317,16 +25118,8 @@
           <t>市道562号線</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25382,39 +25175,44 @@
       </c>
       <c r="R491" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="S491" t="inlineStr">
+      <c r="T491" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T491" t="n">
+      <c r="U491" t="n">
         <v>4063</v>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="V491" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V491" t="n">
+      <c r="W491" t="n">
         <v>5081</v>
       </c>
-      <c r="W491" t="n">
+      <c r="X491" t="n">
         <v>3.9</v>
       </c>
-      <c r="X491" t="inlineStr">
+      <c r="Y491" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y491" t="inlineStr">
+      <c r="Z491" t="inlineStr">
         <is>
           <t>市道562号線</t>
         </is>
       </c>
-      <c r="Z491" t="inlineStr">
+      <c r="AA491" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -25431,16 +25229,8 @@
           <t>市道371号線</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25496,39 +25286,44 @@
       </c>
       <c r="R492" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S492" t="inlineStr">
+      <c r="T492" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T492" t="n">
+      <c r="U492" t="n">
         <v>4063</v>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="V492" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V492" t="n">
+      <c r="W492" t="n">
         <v>5081</v>
       </c>
-      <c r="W492" t="n">
+      <c r="X492" t="n">
         <v>3.9</v>
       </c>
-      <c r="X492" t="inlineStr">
+      <c r="Y492" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y492" t="inlineStr">
+      <c r="Z492" t="inlineStr">
         <is>
           <t>市道371号線</t>
         </is>
       </c>
-      <c r="Z492" t="inlineStr">
+      <c r="AA492" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -25545,16 +25340,8 @@
           <t>市道86号線</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25610,39 +25397,44 @@
       </c>
       <c r="R493" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="S493" t="inlineStr">
+      <c r="T493" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T493" t="n">
+      <c r="U493" t="n">
         <v>4063</v>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="V493" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V493" t="n">
+      <c r="W493" t="n">
         <v>5081</v>
       </c>
-      <c r="W493" t="n">
+      <c r="X493" t="n">
         <v>3.9</v>
       </c>
-      <c r="X493" t="inlineStr">
+      <c r="Y493" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y493" t="inlineStr">
+      <c r="Z493" t="inlineStr">
         <is>
           <t>市道86号線</t>
         </is>
       </c>
-      <c r="Z493" t="inlineStr">
+      <c r="AA493" t="inlineStr">
         <is>
           <t>66</t>
         </is>
@@ -25659,16 +25451,8 @@
           <t>市道509号線</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25724,39 +25508,44 @@
       </c>
       <c r="R494" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="S494" t="inlineStr">
+      <c r="T494" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T494" t="n">
+      <c r="U494" t="n">
         <v>4063</v>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="V494" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V494" t="n">
+      <c r="W494" t="n">
         <v>5081</v>
       </c>
-      <c r="W494" t="n">
+      <c r="X494" t="n">
         <v>3.9</v>
       </c>
-      <c r="X494" t="inlineStr">
+      <c r="Y494" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y494" t="inlineStr">
+      <c r="Z494" t="inlineStr">
         <is>
           <t>市道509号線</t>
         </is>
       </c>
-      <c r="Z494" t="inlineStr">
+      <c r="AA494" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -25773,16 +25562,8 @@
           <t>市道421号線</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25838,39 +25619,44 @@
       </c>
       <c r="R495" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="S495" t="inlineStr">
+      <c r="T495" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T495" t="n">
+      <c r="U495" t="n">
         <v>4063</v>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="V495" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V495" t="n">
+      <c r="W495" t="n">
         <v>5081</v>
       </c>
-      <c r="W495" t="n">
+      <c r="X495" t="n">
         <v>3.9</v>
       </c>
-      <c r="X495" t="inlineStr">
+      <c r="Y495" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y495" t="inlineStr">
+      <c r="Z495" t="inlineStr">
         <is>
           <t>市道421号線</t>
         </is>
       </c>
-      <c r="Z495" t="inlineStr">
+      <c r="AA495" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -25887,16 +25673,8 @@
           <t>市道488号線</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr"/>
       <c r="E496" s="3" t="n">
         <v>46218</v>
       </c>
@@ -25952,39 +25730,44 @@
       </c>
       <c r="R496" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="S496" t="inlineStr">
+      <c r="T496" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T496" t="n">
+      <c r="U496" t="n">
         <v>4063</v>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="V496" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V496" t="n">
+      <c r="W496" t="n">
         <v>5081</v>
       </c>
-      <c r="W496" t="n">
+      <c r="X496" t="n">
         <v>3.9</v>
       </c>
-      <c r="X496" t="inlineStr">
+      <c r="Y496" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y496" t="inlineStr">
+      <c r="Z496" t="inlineStr">
         <is>
           <t>市道488号線</t>
         </is>
       </c>
-      <c r="Z496" t="inlineStr">
+      <c r="AA496" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -26001,16 +25784,8 @@
           <t>市道88号線</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26066,39 +25841,44 @@
       </c>
       <c r="R497" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="S497" t="inlineStr">
+      <c r="T497" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T497" t="n">
+      <c r="U497" t="n">
         <v>4063</v>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="V497" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V497" t="n">
+      <c r="W497" t="n">
         <v>5081</v>
       </c>
-      <c r="W497" t="n">
+      <c r="X497" t="n">
         <v>3.9</v>
       </c>
-      <c r="X497" t="inlineStr">
+      <c r="Y497" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y497" t="inlineStr">
+      <c r="Z497" t="inlineStr">
         <is>
           <t>市道88号線</t>
         </is>
       </c>
-      <c r="Z497" t="inlineStr">
+      <c r="AA497" t="inlineStr">
         <is>
           <t>67</t>
         </is>
@@ -26115,16 +25895,8 @@
           <t>市道429号線</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
       <c r="E498" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26180,39 +25952,44 @@
       </c>
       <c r="R498" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="S498" t="inlineStr">
+      <c r="T498" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T498" t="n">
+      <c r="U498" t="n">
         <v>4063</v>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="V498" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V498" t="n">
+      <c r="W498" t="n">
         <v>5081</v>
       </c>
-      <c r="W498" t="n">
+      <c r="X498" t="n">
         <v>3.9</v>
       </c>
-      <c r="X498" t="inlineStr">
+      <c r="Y498" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y498" t="inlineStr">
+      <c r="Z498" t="inlineStr">
         <is>
           <t>市道429号線</t>
         </is>
       </c>
-      <c r="Z498" t="inlineStr">
+      <c r="AA498" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -26229,16 +26006,8 @@
           <t>市道533号線</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26294,39 +26063,44 @@
       </c>
       <c r="R499" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="S499" t="inlineStr">
+      <c r="T499" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T499" t="n">
+      <c r="U499" t="n">
         <v>4063</v>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="V499" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V499" t="n">
+      <c r="W499" t="n">
         <v>5081</v>
       </c>
-      <c r="W499" t="n">
+      <c r="X499" t="n">
         <v>3.9</v>
       </c>
-      <c r="X499" t="inlineStr">
+      <c r="Y499" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y499" t="inlineStr">
+      <c r="Z499" t="inlineStr">
         <is>
           <t>市道533号線</t>
         </is>
       </c>
-      <c r="Z499" t="inlineStr">
+      <c r="AA499" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -26343,16 +26117,8 @@
           <t>市道534号線</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26408,39 +26174,44 @@
       </c>
       <c r="R500" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="S500" t="inlineStr">
+      <c r="T500" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T500" t="n">
+      <c r="U500" t="n">
         <v>4063</v>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="V500" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V500" t="n">
+      <c r="W500" t="n">
         <v>5081</v>
       </c>
-      <c r="W500" t="n">
+      <c r="X500" t="n">
         <v>3.9</v>
       </c>
-      <c r="X500" t="inlineStr">
+      <c r="Y500" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y500" t="inlineStr">
+      <c r="Z500" t="inlineStr">
         <is>
           <t>市道534号線</t>
         </is>
       </c>
-      <c r="Z500" t="inlineStr">
+      <c r="AA500" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -26457,16 +26228,8 @@
           <t>市道538号線</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26522,39 +26285,44 @@
       </c>
       <c r="R501" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="S501" t="inlineStr">
+      <c r="T501" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T501" t="n">
+      <c r="U501" t="n">
         <v>4063</v>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="V501" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V501" t="n">
+      <c r="W501" t="n">
         <v>5081</v>
       </c>
-      <c r="W501" t="n">
+      <c r="X501" t="n">
         <v>3.9</v>
       </c>
-      <c r="X501" t="inlineStr">
+      <c r="Y501" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y501" t="inlineStr">
+      <c r="Z501" t="inlineStr">
         <is>
           <t>市道538号線</t>
         </is>
       </c>
-      <c r="Z501" t="inlineStr">
+      <c r="AA501" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -26571,16 +26339,8 @@
           <t>市道544号線</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26628,37 +26388,42 @@
       </c>
       <c r="R502" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="S502" t="inlineStr">
+      <c r="T502" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T502" t="n">
+      <c r="U502" t="n">
         <v>4063</v>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="V502" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V502" t="n">
+      <c r="W502" t="n">
         <v>5081</v>
       </c>
-      <c r="W502" t="inlineStr"/>
-      <c r="X502" t="inlineStr">
+      <c r="X502" t="inlineStr"/>
+      <c r="Y502" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y502" t="inlineStr">
+      <c r="Z502" t="inlineStr">
         <is>
           <t>市道544号線</t>
         </is>
       </c>
-      <c r="Z502" t="inlineStr">
+      <c r="AA502" t="inlineStr">
         <is>
           <t>309</t>
         </is>
@@ -26675,16 +26440,8 @@
           <t>市道677号線</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26740,39 +26497,44 @@
       </c>
       <c r="R503" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S503" t="inlineStr">
+      <c r="T503" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T503" t="n">
+      <c r="U503" t="n">
         <v>4063</v>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="V503" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V503" t="n">
+      <c r="W503" t="n">
         <v>5081</v>
       </c>
-      <c r="W503" t="n">
+      <c r="X503" t="n">
         <v>3.9</v>
       </c>
-      <c r="X503" t="inlineStr">
+      <c r="Y503" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y503" t="inlineStr">
+      <c r="Z503" t="inlineStr">
         <is>
           <t>市道677号線</t>
         </is>
       </c>
-      <c r="Z503" t="inlineStr">
+      <c r="AA503" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -26789,16 +26551,8 @@
           <t>市道580号線</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr"/>
       <c r="E504" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26854,39 +26608,44 @@
       </c>
       <c r="R504" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="S504" t="inlineStr">
+      <c r="T504" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T504" t="n">
+      <c r="U504" t="n">
         <v>4063</v>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="V504" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V504" t="n">
+      <c r="W504" t="n">
         <v>5081</v>
       </c>
-      <c r="W504" t="n">
+      <c r="X504" t="n">
         <v>3.9</v>
       </c>
-      <c r="X504" t="inlineStr">
+      <c r="Y504" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y504" t="inlineStr">
+      <c r="Z504" t="inlineStr">
         <is>
           <t>市道580号線</t>
         </is>
       </c>
-      <c r="Z504" t="inlineStr">
+      <c r="AA504" t="inlineStr">
         <is>
           <t>51</t>
         </is>
@@ -26903,16 +26662,8 @@
           <t>市道575号線</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" s="3" t="n">
         <v>46218</v>
       </c>
@@ -26968,39 +26719,44 @@
       </c>
       <c r="R505" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S505" t="inlineStr">
+      <c r="T505" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T505" t="n">
+      <c r="U505" t="n">
         <v>4063</v>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="V505" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V505" t="n">
+      <c r="W505" t="n">
         <v>5081</v>
       </c>
-      <c r="W505" t="n">
+      <c r="X505" t="n">
         <v>3.9</v>
       </c>
-      <c r="X505" t="inlineStr">
+      <c r="Y505" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y505" t="inlineStr">
+      <c r="Z505" t="inlineStr">
         <is>
           <t>市道575号線</t>
         </is>
       </c>
-      <c r="Z505" t="inlineStr">
+      <c r="AA505" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -27017,16 +26773,8 @@
           <t>市道650号線</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27082,39 +26830,44 @@
       </c>
       <c r="R506" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="S506" t="inlineStr">
+      <c r="T506" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T506" t="n">
+      <c r="U506" t="n">
         <v>4063</v>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="V506" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V506" t="n">
+      <c r="W506" t="n">
         <v>5081</v>
       </c>
-      <c r="W506" t="n">
+      <c r="X506" t="n">
         <v>3.9</v>
       </c>
-      <c r="X506" t="inlineStr">
+      <c r="Y506" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y506" t="inlineStr">
+      <c r="Z506" t="inlineStr">
         <is>
           <t>市道650号線</t>
         </is>
       </c>
-      <c r="Z506" t="inlineStr">
+      <c r="AA506" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -27131,16 +26884,8 @@
           <t>市道674号線</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr"/>
       <c r="E507" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27196,39 +26941,44 @@
       </c>
       <c r="R507" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="S507" t="inlineStr">
+      <c r="T507" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T507" t="n">
+      <c r="U507" t="n">
         <v>4063</v>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="V507" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V507" t="n">
+      <c r="W507" t="n">
         <v>5081</v>
       </c>
-      <c r="W507" t="n">
+      <c r="X507" t="n">
         <v>3.9</v>
       </c>
-      <c r="X507" t="inlineStr">
+      <c r="Y507" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y507" t="inlineStr">
+      <c r="Z507" t="inlineStr">
         <is>
           <t>市道674号線</t>
         </is>
       </c>
-      <c r="Z507" t="inlineStr">
+      <c r="AA507" t="inlineStr">
         <is>
           <t>59</t>
         </is>
@@ -27245,16 +26995,8 @@
           <t>市道471号線</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr"/>
       <c r="E508" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27310,39 +27052,44 @@
       </c>
       <c r="R508" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S508" t="inlineStr">
+      <c r="T508" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T508" t="n">
+      <c r="U508" t="n">
         <v>4063</v>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="V508" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V508" t="n">
+      <c r="W508" t="n">
         <v>5081</v>
       </c>
-      <c r="W508" t="n">
+      <c r="X508" t="n">
         <v>3.9</v>
       </c>
-      <c r="X508" t="inlineStr">
+      <c r="Y508" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y508" t="inlineStr">
+      <c r="Z508" t="inlineStr">
         <is>
           <t>市道471号線</t>
         </is>
       </c>
-      <c r="Z508" t="inlineStr">
+      <c r="AA508" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -27359,16 +27106,8 @@
           <t>市道603号線</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C509" t="inlineStr"/>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27424,39 +27163,44 @@
       </c>
       <c r="R509" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="S509" t="inlineStr">
+      <c r="T509" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T509" t="n">
+      <c r="U509" t="n">
         <v>4063</v>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="V509" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V509" t="n">
+      <c r="W509" t="n">
         <v>5081</v>
       </c>
-      <c r="W509" t="n">
+      <c r="X509" t="n">
         <v>3.9</v>
       </c>
-      <c r="X509" t="inlineStr">
+      <c r="Y509" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y509" t="inlineStr">
+      <c r="Z509" t="inlineStr">
         <is>
           <t>市道603号線</t>
         </is>
       </c>
-      <c r="Z509" t="inlineStr">
+      <c r="AA509" t="inlineStr">
         <is>
           <t>53</t>
         </is>
@@ -27473,16 +27217,8 @@
           <t>市道656号線</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C510" t="inlineStr"/>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27538,39 +27274,44 @@
       </c>
       <c r="R510" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="S510" t="inlineStr">
+      <c r="T510" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T510" t="n">
+      <c r="U510" t="n">
         <v>4063</v>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="V510" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V510" t="n">
+      <c r="W510" t="n">
         <v>5081</v>
       </c>
-      <c r="W510" t="n">
+      <c r="X510" t="n">
         <v>3.9</v>
       </c>
-      <c r="X510" t="inlineStr">
+      <c r="Y510" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y510" t="inlineStr">
+      <c r="Z510" t="inlineStr">
         <is>
           <t>市道656号線</t>
         </is>
       </c>
-      <c r="Z510" t="inlineStr">
+      <c r="AA510" t="inlineStr">
         <is>
           <t>56</t>
         </is>
@@ -27587,16 +27328,8 @@
           <t>市道686号線</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27652,39 +27385,44 @@
       </c>
       <c r="R511" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="S511" t="inlineStr">
+      <c r="T511" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T511" t="n">
+      <c r="U511" t="n">
         <v>4063</v>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="V511" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V511" t="n">
+      <c r="W511" t="n">
         <v>5081</v>
       </c>
-      <c r="W511" t="n">
+      <c r="X511" t="n">
         <v>3.9</v>
       </c>
-      <c r="X511" t="inlineStr">
+      <c r="Y511" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y511" t="inlineStr">
+      <c r="Z511" t="inlineStr">
         <is>
           <t>市道686号線</t>
         </is>
       </c>
-      <c r="Z511" t="inlineStr">
+      <c r="AA511" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -27701,16 +27439,8 @@
           <t>市道363号線</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C512" t="inlineStr"/>
+      <c r="D512" t="inlineStr"/>
       <c r="E512" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27766,39 +27496,44 @@
       </c>
       <c r="R512" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S512" t="inlineStr">
+      <c r="T512" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T512" t="n">
+      <c r="U512" t="n">
         <v>4063</v>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="V512" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V512" t="n">
+      <c r="W512" t="n">
         <v>5081</v>
       </c>
-      <c r="W512" t="n">
+      <c r="X512" t="n">
         <v>3.9</v>
       </c>
-      <c r="X512" t="inlineStr">
+      <c r="Y512" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y512" t="inlineStr">
+      <c r="Z512" t="inlineStr">
         <is>
           <t>市道363号線</t>
         </is>
       </c>
-      <c r="Z512" t="inlineStr">
+      <c r="AA512" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -27815,16 +27550,8 @@
           <t>市道79号線</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr"/>
       <c r="E513" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27880,39 +27607,44 @@
       </c>
       <c r="R513" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="S513" t="inlineStr">
+      <c r="T513" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T513" t="n">
+      <c r="U513" t="n">
         <v>4064</v>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="V513" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V513" t="n">
+      <c r="W513" t="n">
         <v>5854</v>
       </c>
-      <c r="W513" t="n">
+      <c r="X513" t="n">
         <v>4.2</v>
       </c>
-      <c r="X513" t="inlineStr">
+      <c r="Y513" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y513" t="inlineStr">
+      <c r="Z513" t="inlineStr">
         <is>
           <t>市道79号線</t>
         </is>
       </c>
-      <c r="Z513" t="inlineStr">
+      <c r="AA513" t="inlineStr">
         <is>
           <t>86</t>
         </is>
@@ -27929,16 +27661,8 @@
           <t>市道80号線</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr"/>
       <c r="E514" s="3" t="n">
         <v>46218</v>
       </c>
@@ -27994,39 +27718,44 @@
       </c>
       <c r="R514" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="S514" t="inlineStr">
+      <c r="T514" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T514" t="n">
+      <c r="U514" t="n">
         <v>4064</v>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="V514" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V514" t="n">
+      <c r="W514" t="n">
         <v>5854</v>
       </c>
-      <c r="W514" t="n">
+      <c r="X514" t="n">
         <v>4.2</v>
       </c>
-      <c r="X514" t="inlineStr">
+      <c r="Y514" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y514" t="inlineStr">
+      <c r="Z514" t="inlineStr">
         <is>
           <t>市道80号線</t>
         </is>
       </c>
-      <c r="Z514" t="inlineStr">
+      <c r="AA514" t="inlineStr">
         <is>
           <t>87</t>
         </is>
@@ -28043,16 +27772,8 @@
           <t>市道78号線</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C515" t="inlineStr"/>
+      <c r="D515" t="inlineStr"/>
       <c r="E515" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28108,39 +27829,44 @@
       </c>
       <c r="R515" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="S515" t="inlineStr">
+      <c r="T515" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T515" t="n">
+      <c r="U515" t="n">
         <v>4064</v>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="V515" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V515" t="n">
+      <c r="W515" t="n">
         <v>5854</v>
       </c>
-      <c r="W515" t="n">
+      <c r="X515" t="n">
         <v>4.2</v>
       </c>
-      <c r="X515" t="inlineStr">
+      <c r="Y515" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y515" t="inlineStr">
+      <c r="Z515" t="inlineStr">
         <is>
           <t>市道78号線</t>
         </is>
       </c>
-      <c r="Z515" t="inlineStr">
+      <c r="AA515" t="inlineStr">
         <is>
           <t>85</t>
         </is>
@@ -28157,16 +27883,8 @@
           <t>市道77号線</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr"/>
       <c r="E516" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28222,39 +27940,44 @@
       </c>
       <c r="R516" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="S516" t="inlineStr">
+      <c r="T516" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T516" t="n">
+      <c r="U516" t="n">
         <v>4064</v>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="V516" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V516" t="n">
+      <c r="W516" t="n">
         <v>5854</v>
       </c>
-      <c r="W516" t="n">
+      <c r="X516" t="n">
         <v>4.2</v>
       </c>
-      <c r="X516" t="inlineStr">
+      <c r="Y516" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y516" t="inlineStr">
+      <c r="Z516" t="inlineStr">
         <is>
           <t>市道77号線</t>
         </is>
       </c>
-      <c r="Z516" t="inlineStr">
+      <c r="AA516" t="inlineStr">
         <is>
           <t>84</t>
         </is>
@@ -28271,16 +27994,8 @@
           <t>市道76号線</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr"/>
       <c r="E517" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28336,39 +28051,44 @@
       </c>
       <c r="R517" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="S517" t="inlineStr">
+      <c r="T517" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T517" t="n">
+      <c r="U517" t="n">
         <v>4064</v>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="V517" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V517" t="n">
+      <c r="W517" t="n">
         <v>5854</v>
       </c>
-      <c r="W517" t="n">
+      <c r="X517" t="n">
         <v>4.2</v>
       </c>
-      <c r="X517" t="inlineStr">
+      <c r="Y517" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y517" t="inlineStr">
+      <c r="Z517" t="inlineStr">
         <is>
           <t>市道76号線</t>
         </is>
       </c>
-      <c r="Z517" t="inlineStr">
+      <c r="AA517" t="inlineStr">
         <is>
           <t>83</t>
         </is>
@@ -28385,16 +28105,8 @@
           <t>市道73号線</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr"/>
       <c r="E518" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28440,35 +28152,40 @@
       </c>
       <c r="R518" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="S518" t="inlineStr">
+      <c r="T518" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T518" t="n">
+      <c r="U518" t="n">
         <v>4064</v>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="V518" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V518" t="inlineStr"/>
       <c r="W518" t="inlineStr"/>
-      <c r="X518" t="inlineStr">
+      <c r="X518" t="inlineStr"/>
+      <c r="Y518" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y518" t="inlineStr">
+      <c r="Z518" t="inlineStr">
         <is>
           <t>市道73号線</t>
         </is>
       </c>
-      <c r="Z518" t="inlineStr">
+      <c r="AA518" t="inlineStr">
         <is>
           <t>310</t>
         </is>
@@ -28485,16 +28202,8 @@
           <t>市道75号線</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr"/>
       <c r="E519" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28550,39 +28259,44 @@
       </c>
       <c r="R519" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="S519" t="inlineStr">
+      <c r="T519" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T519" t="n">
+      <c r="U519" t="n">
         <v>4064</v>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="V519" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V519" t="n">
+      <c r="W519" t="n">
         <v>5854</v>
       </c>
-      <c r="W519" t="n">
+      <c r="X519" t="n">
         <v>4.2</v>
       </c>
-      <c r="X519" t="inlineStr">
+      <c r="Y519" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y519" t="inlineStr">
+      <c r="Z519" t="inlineStr">
         <is>
           <t>市道75号線</t>
         </is>
       </c>
-      <c r="Z519" t="inlineStr">
+      <c r="AA519" t="inlineStr">
         <is>
           <t>82</t>
         </is>
@@ -28599,16 +28313,8 @@
           <t>市道13号線</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr"/>
       <c r="E520" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28664,39 +28370,44 @@
       </c>
       <c r="R520" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="S520" t="inlineStr">
+      <c r="T520" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T520" t="n">
+      <c r="U520" t="n">
         <v>4064</v>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="V520" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V520" t="n">
+      <c r="W520" t="n">
         <v>5854</v>
       </c>
-      <c r="W520" t="n">
+      <c r="X520" t="n">
         <v>4.2</v>
       </c>
-      <c r="X520" t="inlineStr">
+      <c r="Y520" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y520" t="inlineStr">
+      <c r="Z520" t="inlineStr">
         <is>
           <t>市道13号線</t>
         </is>
       </c>
-      <c r="Z520" t="inlineStr">
+      <c r="AA520" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -28713,16 +28424,8 @@
           <t>市道69号線</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr"/>
       <c r="E521" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28778,39 +28481,44 @@
       </c>
       <c r="R521" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="S521" t="inlineStr">
+      <c r="T521" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T521" t="n">
+      <c r="U521" t="n">
         <v>4064</v>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="V521" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V521" t="n">
+      <c r="W521" t="n">
         <v>5854</v>
       </c>
-      <c r="W521" t="n">
+      <c r="X521" t="n">
         <v>4.2</v>
       </c>
-      <c r="X521" t="inlineStr">
+      <c r="Y521" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y521" t="inlineStr">
+      <c r="Z521" t="inlineStr">
         <is>
           <t>市道69号線</t>
         </is>
       </c>
-      <c r="Z521" t="inlineStr">
+      <c r="AA521" t="inlineStr">
         <is>
           <t>77</t>
         </is>
@@ -28827,16 +28535,8 @@
           <t>市道68号線</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr"/>
       <c r="E522" s="3" t="n">
         <v>46218</v>
       </c>
@@ -28892,39 +28592,44 @@
       </c>
       <c r="R522" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="S522" t="inlineStr">
+      <c r="T522" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T522" t="n">
+      <c r="U522" t="n">
         <v>4064</v>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="V522" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V522" t="n">
+      <c r="W522" t="n">
         <v>5854</v>
       </c>
-      <c r="W522" t="n">
+      <c r="X522" t="n">
         <v>4.2</v>
       </c>
-      <c r="X522" t="inlineStr">
+      <c r="Y522" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y522" t="inlineStr">
+      <c r="Z522" t="inlineStr">
         <is>
           <t>市道68号線</t>
         </is>
       </c>
-      <c r="Z522" t="inlineStr">
+      <c r="AA522" t="inlineStr">
         <is>
           <t>76</t>
         </is>
@@ -28941,16 +28646,8 @@
           <t>市道64号線</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr"/>
       <c r="E523" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29006,39 +28703,44 @@
       </c>
       <c r="R523" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="S523" t="inlineStr">
+      <c r="T523" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T523" t="n">
+      <c r="U523" t="n">
         <v>4064</v>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="V523" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V523" t="n">
+      <c r="W523" t="n">
         <v>5854</v>
       </c>
-      <c r="W523" t="n">
+      <c r="X523" t="n">
         <v>4.2</v>
       </c>
-      <c r="X523" t="inlineStr">
+      <c r="Y523" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y523" t="inlineStr">
+      <c r="Z523" t="inlineStr">
         <is>
           <t>市道64号線</t>
         </is>
       </c>
-      <c r="Z523" t="inlineStr">
+      <c r="AA523" t="inlineStr">
         <is>
           <t>73</t>
         </is>
@@ -29055,16 +28757,8 @@
           <t>市道65号線</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr"/>
       <c r="E524" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29120,39 +28814,44 @@
       </c>
       <c r="R524" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="S524" t="inlineStr">
+      <c r="T524" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T524" t="n">
+      <c r="U524" t="n">
         <v>4064</v>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="V524" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V524" t="n">
+      <c r="W524" t="n">
         <v>5854</v>
       </c>
-      <c r="W524" t="n">
+      <c r="X524" t="n">
         <v>4.2</v>
       </c>
-      <c r="X524" t="inlineStr">
+      <c r="Y524" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y524" t="inlineStr">
+      <c r="Z524" t="inlineStr">
         <is>
           <t>市道65号線</t>
         </is>
       </c>
-      <c r="Z524" t="inlineStr">
+      <c r="AA524" t="inlineStr">
         <is>
           <t>74</t>
         </is>
@@ -29169,16 +28868,8 @@
           <t>市道61号線</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
       <c r="E525" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29234,39 +28925,44 @@
       </c>
       <c r="R525" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="S525" t="inlineStr">
+      <c r="T525" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T525" t="n">
+      <c r="U525" t="n">
         <v>4064</v>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="V525" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V525" t="n">
+      <c r="W525" t="n">
         <v>5854</v>
       </c>
-      <c r="W525" t="n">
+      <c r="X525" t="n">
         <v>4.2</v>
       </c>
-      <c r="X525" t="inlineStr">
+      <c r="Y525" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y525" t="inlineStr">
+      <c r="Z525" t="inlineStr">
         <is>
           <t>市道61号線</t>
         </is>
       </c>
-      <c r="Z525" t="inlineStr">
+      <c r="AA525" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -29283,16 +28979,8 @@
           <t>市道59号線</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr"/>
       <c r="E526" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29348,39 +29036,44 @@
       </c>
       <c r="R526" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="S526" t="inlineStr">
+      <c r="T526" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T526" t="n">
+      <c r="U526" t="n">
         <v>4064</v>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="V526" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V526" t="n">
+      <c r="W526" t="n">
         <v>5854</v>
       </c>
-      <c r="W526" t="n">
+      <c r="X526" t="n">
         <v>4.2</v>
       </c>
-      <c r="X526" t="inlineStr">
+      <c r="Y526" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y526" t="inlineStr">
+      <c r="Z526" t="inlineStr">
         <is>
           <t>市道59号線</t>
         </is>
       </c>
-      <c r="Z526" t="inlineStr">
+      <c r="AA526" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -29397,16 +29090,8 @@
           <t>市道58号線</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr"/>
       <c r="E527" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29462,39 +29147,44 @@
       </c>
       <c r="R527" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="S527" t="inlineStr">
+      <c r="T527" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T527" t="n">
+      <c r="U527" t="n">
         <v>4064</v>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="V527" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V527" t="n">
+      <c r="W527" t="n">
         <v>5854</v>
       </c>
-      <c r="W527" t="n">
+      <c r="X527" t="n">
         <v>4.2</v>
       </c>
-      <c r="X527" t="inlineStr">
+      <c r="Y527" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y527" t="inlineStr">
+      <c r="Z527" t="inlineStr">
         <is>
           <t>市道58号線</t>
         </is>
       </c>
-      <c r="Z527" t="inlineStr">
+      <c r="AA527" t="inlineStr">
         <is>
           <t>69</t>
         </is>
@@ -29511,16 +29201,8 @@
           <t>市道83号線</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C528" t="inlineStr"/>
+      <c r="D528" t="inlineStr"/>
       <c r="E528" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29576,39 +29258,44 @@
       </c>
       <c r="R528" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="S528" t="inlineStr">
+      <c r="T528" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T528" t="n">
+      <c r="U528" t="n">
         <v>4064</v>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="V528" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V528" t="n">
+      <c r="W528" t="n">
         <v>5854</v>
       </c>
-      <c r="W528" t="n">
+      <c r="X528" t="n">
         <v>4.2</v>
       </c>
-      <c r="X528" t="inlineStr">
+      <c r="Y528" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y528" t="inlineStr">
+      <c r="Z528" t="inlineStr">
         <is>
           <t>市道83号線</t>
         </is>
       </c>
-      <c r="Z528" t="inlineStr">
+      <c r="AA528" t="inlineStr">
         <is>
           <t>88</t>
         </is>
@@ -29625,16 +29312,8 @@
           <t>市道736号線</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C529" t="inlineStr"/>
+      <c r="D529" t="inlineStr"/>
       <c r="E529" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29690,39 +29369,44 @@
       </c>
       <c r="R529" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="S529" t="inlineStr">
+      <c r="T529" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T529" t="n">
+      <c r="U529" t="n">
         <v>4064</v>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="V529" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V529" t="n">
+      <c r="W529" t="n">
         <v>5854</v>
       </c>
-      <c r="W529" t="n">
+      <c r="X529" t="n">
         <v>4.2</v>
       </c>
-      <c r="X529" t="inlineStr">
+      <c r="Y529" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y529" t="inlineStr">
+      <c r="Z529" t="inlineStr">
         <is>
           <t>市道736号線</t>
         </is>
       </c>
-      <c r="Z529" t="inlineStr">
+      <c r="AA529" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -29739,16 +29423,8 @@
           <t>67 見付公園</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>公園復旧工事</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C530" t="inlineStr"/>
+      <c r="D530" t="inlineStr"/>
       <c r="E530" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29794,35 +29470,40 @@
       </c>
       <c r="R530" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="S530" t="inlineStr">
+      <c r="T530" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T530" t="n">
+      <c r="U530" t="n">
         <v>67</v>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="V530" t="inlineStr">
         <is>
           <t>見付公園</t>
         </is>
       </c>
-      <c r="V530" t="inlineStr"/>
       <c r="W530" t="inlineStr"/>
-      <c r="X530" t="inlineStr">
+      <c r="X530" t="inlineStr"/>
+      <c r="Y530" t="inlineStr">
         <is>
           <t>公園復旧工事</t>
         </is>
       </c>
-      <c r="Y530" t="inlineStr">
+      <c r="Z530" t="inlineStr">
         <is>
           <t>67 見付公園</t>
         </is>
       </c>
-      <c r="Z530" t="inlineStr">
+      <c r="AA530" t="inlineStr">
         <is>
           <t>93</t>
         </is>
@@ -29839,16 +29520,8 @@
           <t>市道71号線</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" s="3" t="n">
         <v>46218</v>
       </c>
@@ -29904,39 +29577,44 @@
       </c>
       <c r="R531" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="S531" t="inlineStr">
+      <c r="T531" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T531" t="n">
+      <c r="U531" t="n">
         <v>4064</v>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="V531" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V531" t="n">
+      <c r="W531" t="n">
         <v>5854</v>
       </c>
-      <c r="W531" t="n">
+      <c r="X531" t="n">
         <v>4.2</v>
       </c>
-      <c r="X531" t="inlineStr">
+      <c r="Y531" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y531" t="inlineStr">
+      <c r="Z531" t="inlineStr">
         <is>
           <t>市道71号線</t>
         </is>
       </c>
-      <c r="Z531" t="inlineStr">
+      <c r="AA531" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -29953,16 +29631,8 @@
           <t>市道60号線</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" s="3" t="n">
         <v>46218</v>
       </c>
@@ -30018,39 +29688,44 @@
       </c>
       <c r="R532" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="S532" t="inlineStr">
+      <c r="T532" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T532" t="n">
+      <c r="U532" t="n">
         <v>4064</v>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="V532" t="inlineStr">
         <is>
           <t>珠洲市宝立町地内</t>
         </is>
       </c>
-      <c r="V532" t="n">
+      <c r="W532" t="n">
         <v>5854</v>
       </c>
-      <c r="W532" t="n">
+      <c r="X532" t="n">
         <v>4.2</v>
       </c>
-      <c r="X532" t="inlineStr">
+      <c r="Y532" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y532" t="inlineStr">
+      <c r="Z532" t="inlineStr">
         <is>
           <t>市道60号線</t>
         </is>
       </c>
-      <c r="Z532" t="inlineStr">
+      <c r="AA532" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -30067,16 +29742,8 @@
           <t>市道10号線</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C533" t="inlineStr"/>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" s="3" t="n">
         <v>46218</v>
       </c>
@@ -30132,39 +29799,44 @@
       </c>
       <c r="R533" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S533" t="inlineStr">
+      <c r="T533" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T533" t="n">
+      <c r="U533" t="n">
         <v>3889</v>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="V533" t="inlineStr">
         <is>
           <t>珠洲市宝立町春日野 地内</t>
         </is>
       </c>
-      <c r="V533" t="n">
+      <c r="W533" t="n">
         <v>828</v>
       </c>
-      <c r="W533" t="n">
+      <c r="X533" t="n">
         <v>6.2</v>
       </c>
-      <c r="X533" t="inlineStr">
+      <c r="Y533" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y533" t="inlineStr">
+      <c r="Z533" t="inlineStr">
         <is>
           <t>市道10号線</t>
         </is>
       </c>
-      <c r="Z533" t="inlineStr">
+      <c r="AA533" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -30181,16 +29853,8 @@
           <t>市道52-2号線</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>道路復旧工事</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>道路規制</t>
-        </is>
-      </c>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr"/>
       <c r="E534" s="3" t="n">
         <v>46218</v>
       </c>
@@ -30246,39 +29910,44 @@
       </c>
       <c r="R534" t="inlineStr">
         <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S534" t="inlineStr">
+      <c r="T534" t="inlineStr">
         <is>
           <t>査定番号</t>
         </is>
       </c>
-      <c r="T534" t="n">
+      <c r="U534" t="n">
         <v>3892</v>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="V534" t="inlineStr">
         <is>
           <t>珠洲市宝立町鵜島～鵜飼 地内</t>
         </is>
       </c>
-      <c r="V534" t="n">
+      <c r="W534" t="n">
         <v>514</v>
       </c>
-      <c r="W534" t="n">
+      <c r="X534" t="n">
         <v>11.1</v>
       </c>
-      <c r="X534" t="inlineStr">
+      <c r="Y534" t="inlineStr">
         <is>
           <t>道路復旧工事</t>
         </is>
       </c>
-      <c r="Y534" t="inlineStr">
+      <c r="Z534" t="inlineStr">
         <is>
           <t>市道52-2号線</t>
         </is>
       </c>
-      <c r="Z534" t="inlineStr">
+      <c r="AA534" t="inlineStr">
         <is>
           <t>16</t>
         </is>
